--- a/assets/inventory/excel/רשימה 2.xlsx
+++ b/assets/inventory/excel/רשימה 2.xlsx
@@ -1,21 +1,20 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="6" lowestEdited="7" rupBuild="14420"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://eldad-my.sharepoint.com/personal/nave_reouel_com/Documents/מסמכים/פיתוח/hightide/assets/inventory/excel/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="23" documentId="11_D59710881FE11F9269A083521B532902419DE227" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{952B5FEA-A5EF-4498-A05A-354A1FF4E047}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="1960" windowHeight="0"/>
   </bookViews>
   <sheets>
     <sheet name="רשימת מכנסיים" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="162913"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
@@ -33,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="23" uniqueCount="18">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="27" uniqueCount="20">
   <si>
     <t>רשימת מכנסיים</t>
   </si>
@@ -87,12 +86,18 @@
   </si>
   <si>
     <t>T&amp;C SHIRTS</t>
+  </si>
+  <si>
+    <t>#31</t>
+  </si>
+  <si>
+    <t>m</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
   <fonts count="5">
     <font>
       <sz val="11"/>
@@ -398,12 +403,12 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="PantsTable" displayName="PantsTable" ref="A3:D30">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="PantsTable" displayName="PantsTable" ref="A3:D30">
   <tableColumns count="4">
-    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="מספר מכנס"/>
-    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" name="שם מכנס"/>
-    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0000-000003000000}" name="מידה"/>
-    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0000-000004000000}" name="תאריך" dataDxfId="0">
+    <tableColumn id="1" name="מספר מכנס"/>
+    <tableColumn id="2" name="שם מכנס"/>
+    <tableColumn id="3" name="מידה"/>
+    <tableColumn id="4" name="תאריך" dataDxfId="0">
       <calculatedColumnFormula>$K$2</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -559,19 +564,19 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:K30"/>
-  <sheetFormatPr defaultRowHeight="13.8"/>
+  <sheetFormatPr defaultRowHeight="14"/>
   <cols>
     <col min="1" max="1" width="15" customWidth="1"/>
     <col min="2" max="2" width="22" customWidth="1"/>
     <col min="3" max="3" width="12" customWidth="1"/>
     <col min="4" max="4" width="15.5" customWidth="1"/>
-    <col min="5" max="5" width="12.59765625" customWidth="1"/>
-    <col min="6" max="6" width="9.8984375" style="23" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="9.59765625" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="9.69921875" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="9.69921875" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="12.58203125" customWidth="1"/>
+    <col min="6" max="6" width="9.9140625" style="23" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="9.58203125" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="9.6640625" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="9.6640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:11" ht="24" customHeight="1">
@@ -589,7 +594,7 @@
         <v>46217</v>
       </c>
     </row>
-    <row r="3" spans="1:11" ht="19.2" customHeight="1" thickTop="1">
+    <row r="3" spans="1:11" ht="19.25" customHeight="1" thickTop="1">
       <c r="A3" s="1" t="s">
         <v>2</v>
       </c>
@@ -609,7 +614,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="4" spans="1:11" ht="16.8" customHeight="1">
+    <row r="4" spans="1:11" ht="16.75" customHeight="1">
       <c r="A4" s="7" t="s">
         <v>11</v>
       </c>
@@ -632,7 +637,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="5" spans="1:11" ht="16.8" customHeight="1">
+    <row r="5" spans="1:11" ht="16.75" customHeight="1">
       <c r="A5" s="8" t="s">
         <v>14</v>
       </c>
@@ -655,7 +660,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="6" spans="1:11" ht="16.8" customHeight="1">
+    <row r="6" spans="1:11" ht="16.75" customHeight="1">
       <c r="A6" s="8" t="s">
         <v>16</v>
       </c>
@@ -678,15 +683,27 @@
         <v>8</v>
       </c>
     </row>
-    <row r="7" spans="1:11" ht="16.8" customHeight="1">
-      <c r="A7" s="8"/>
-      <c r="B7" s="5"/>
-      <c r="C7" s="11"/>
-      <c r="D7" s="18"/>
-      <c r="E7" s="19"/>
-      <c r="F7" s="22"/>
-    </row>
-    <row r="8" spans="1:11" ht="16.8" customHeight="1">
+    <row r="7" spans="1:11" ht="16.75" customHeight="1">
+      <c r="A7" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="B7" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="C7" s="11" t="s">
+        <v>19</v>
+      </c>
+      <c r="D7" s="18">
+        <v>46218</v>
+      </c>
+      <c r="E7" s="19" t="s">
+        <v>8</v>
+      </c>
+      <c r="F7" s="22">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="8" spans="1:11" ht="16.75" customHeight="1">
       <c r="A8" s="8"/>
       <c r="B8" s="5"/>
       <c r="C8" s="11"/>
@@ -694,7 +711,7 @@
       <c r="E8" s="20"/>
       <c r="F8" s="21"/>
     </row>
-    <row r="9" spans="1:11" ht="16.8" customHeight="1">
+    <row r="9" spans="1:11" ht="16.75" customHeight="1">
       <c r="A9" s="8"/>
       <c r="B9" s="5"/>
       <c r="C9" s="11"/>
@@ -702,7 +719,7 @@
       <c r="E9" s="19"/>
       <c r="F9" s="22"/>
     </row>
-    <row r="10" spans="1:11" ht="16.8" customHeight="1">
+    <row r="10" spans="1:11" ht="16.75" customHeight="1">
       <c r="A10" s="8"/>
       <c r="B10" s="5"/>
       <c r="C10" s="11"/>
@@ -710,7 +727,7 @@
       <c r="E10" s="20"/>
       <c r="F10" s="21"/>
     </row>
-    <row r="11" spans="1:11" ht="16.8" customHeight="1">
+    <row r="11" spans="1:11" ht="16.75" customHeight="1">
       <c r="A11" s="8"/>
       <c r="B11" s="5"/>
       <c r="C11" s="11"/>
@@ -718,7 +735,7 @@
       <c r="E11" s="19"/>
       <c r="F11" s="22"/>
     </row>
-    <row r="12" spans="1:11" ht="16.8" customHeight="1">
+    <row r="12" spans="1:11" ht="16.75" customHeight="1">
       <c r="A12" s="8"/>
       <c r="B12" s="5"/>
       <c r="C12" s="11"/>
@@ -726,7 +743,7 @@
       <c r="E12" s="20"/>
       <c r="F12" s="21"/>
     </row>
-    <row r="13" spans="1:11" ht="16.8" customHeight="1">
+    <row r="13" spans="1:11" ht="16.75" customHeight="1">
       <c r="A13" s="8"/>
       <c r="B13" s="5"/>
       <c r="C13" s="11"/>
@@ -734,7 +751,7 @@
       <c r="E13" s="19"/>
       <c r="F13" s="22"/>
     </row>
-    <row r="14" spans="1:11" ht="16.8" customHeight="1">
+    <row r="14" spans="1:11" ht="16.75" customHeight="1">
       <c r="A14" s="8"/>
       <c r="B14" s="5"/>
       <c r="C14" s="11"/>
@@ -742,7 +759,7 @@
       <c r="E14" s="20"/>
       <c r="F14" s="21"/>
     </row>
-    <row r="15" spans="1:11" ht="16.8" customHeight="1">
+    <row r="15" spans="1:11" ht="16.75" customHeight="1">
       <c r="A15" s="8"/>
       <c r="B15" s="5"/>
       <c r="C15" s="11"/>
@@ -750,7 +767,7 @@
       <c r="E15" s="19"/>
       <c r="F15" s="22"/>
     </row>
-    <row r="16" spans="1:11" ht="16.8" customHeight="1">
+    <row r="16" spans="1:11" ht="16.75" customHeight="1">
       <c r="A16" s="8"/>
       <c r="B16" s="5"/>
       <c r="C16" s="11"/>
@@ -758,7 +775,7 @@
       <c r="E16" s="20"/>
       <c r="F16" s="21"/>
     </row>
-    <row r="17" spans="1:6" ht="16.8" customHeight="1">
+    <row r="17" spans="1:6" ht="16.75" customHeight="1">
       <c r="A17" s="8"/>
       <c r="B17" s="5"/>
       <c r="C17" s="11"/>
@@ -766,7 +783,7 @@
       <c r="E17" s="19"/>
       <c r="F17" s="22"/>
     </row>
-    <row r="18" spans="1:6" ht="16.8" customHeight="1">
+    <row r="18" spans="1:6" ht="16.75" customHeight="1">
       <c r="A18" s="8"/>
       <c r="B18" s="5"/>
       <c r="C18" s="11"/>
@@ -774,7 +791,7 @@
       <c r="E18" s="20"/>
       <c r="F18" s="21"/>
     </row>
-    <row r="19" spans="1:6" ht="16.8" customHeight="1">
+    <row r="19" spans="1:6" ht="16.75" customHeight="1">
       <c r="A19" s="8"/>
       <c r="B19" s="5"/>
       <c r="C19" s="11"/>
@@ -782,7 +799,7 @@
       <c r="E19" s="19"/>
       <c r="F19" s="22"/>
     </row>
-    <row r="20" spans="1:6" ht="16.8" customHeight="1">
+    <row r="20" spans="1:6" ht="16.75" customHeight="1">
       <c r="A20" s="8"/>
       <c r="B20" s="5"/>
       <c r="C20" s="11"/>
@@ -790,7 +807,7 @@
       <c r="E20" s="20"/>
       <c r="F20" s="21"/>
     </row>
-    <row r="21" spans="1:6" ht="16.8" customHeight="1">
+    <row r="21" spans="1:6" ht="16.75" customHeight="1">
       <c r="A21" s="8"/>
       <c r="B21" s="5"/>
       <c r="C21" s="11"/>
@@ -798,7 +815,7 @@
       <c r="E21" s="19"/>
       <c r="F21" s="22"/>
     </row>
-    <row r="22" spans="1:6" ht="16.8" customHeight="1">
+    <row r="22" spans="1:6" ht="16.75" customHeight="1">
       <c r="A22" s="8"/>
       <c r="B22" s="5"/>
       <c r="C22" s="11"/>
@@ -806,7 +823,7 @@
       <c r="E22" s="20"/>
       <c r="F22" s="21"/>
     </row>
-    <row r="23" spans="1:6" ht="16.8" customHeight="1">
+    <row r="23" spans="1:6" ht="16.75" customHeight="1">
       <c r="A23" s="8"/>
       <c r="B23" s="5"/>
       <c r="C23" s="11"/>
@@ -814,7 +831,7 @@
       <c r="E23" s="19"/>
       <c r="F23" s="22"/>
     </row>
-    <row r="24" spans="1:6" ht="16.8" customHeight="1">
+    <row r="24" spans="1:6" ht="16.75" customHeight="1">
       <c r="A24" s="8"/>
       <c r="B24" s="5"/>
       <c r="C24" s="11"/>
@@ -822,7 +839,7 @@
       <c r="E24" s="20"/>
       <c r="F24" s="21"/>
     </row>
-    <row r="25" spans="1:6" ht="16.8" customHeight="1">
+    <row r="25" spans="1:6" ht="16.75" customHeight="1">
       <c r="A25" s="8"/>
       <c r="B25" s="5"/>
       <c r="C25" s="11"/>
@@ -830,7 +847,7 @@
       <c r="E25" s="19"/>
       <c r="F25" s="22"/>
     </row>
-    <row r="26" spans="1:6" ht="16.8" customHeight="1">
+    <row r="26" spans="1:6" ht="16.75" customHeight="1">
       <c r="A26" s="8"/>
       <c r="B26" s="5"/>
       <c r="C26" s="11"/>
@@ -838,7 +855,7 @@
       <c r="E26" s="20"/>
       <c r="F26" s="21"/>
     </row>
-    <row r="27" spans="1:6" ht="16.8" customHeight="1">
+    <row r="27" spans="1:6" ht="16.75" customHeight="1">
       <c r="A27" s="8"/>
       <c r="B27" s="5"/>
       <c r="C27" s="11"/>
@@ -846,7 +863,7 @@
       <c r="E27" s="19"/>
       <c r="F27" s="22"/>
     </row>
-    <row r="28" spans="1:6" ht="16.8" customHeight="1">
+    <row r="28" spans="1:6" ht="16.75" customHeight="1">
       <c r="A28" s="8"/>
       <c r="B28" s="5"/>
       <c r="C28" s="11"/>
@@ -854,7 +871,7 @@
       <c r="E28" s="20"/>
       <c r="F28" s="21"/>
     </row>
-    <row r="29" spans="1:6" ht="16.8" customHeight="1">
+    <row r="29" spans="1:6" ht="16.75" customHeight="1">
       <c r="A29" s="8"/>
       <c r="B29" s="5"/>
       <c r="C29" s="11"/>
@@ -862,7 +879,7 @@
       <c r="E29" s="19"/>
       <c r="F29" s="22"/>
     </row>
-    <row r="30" spans="1:6" ht="16.8" customHeight="1">
+    <row r="30" spans="1:6" ht="16.75" customHeight="1">
       <c r="A30" s="9"/>
       <c r="B30" s="6"/>
       <c r="C30" s="12"/>
@@ -875,7 +892,7 @@
     <mergeCell ref="A1:C1"/>
   </mergeCells>
   <dataValidations count="1">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E4:E30" xr:uid="{00000000-0002-0000-0000-000000000000}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E4:E30">
       <formula1>$K$5:$K$6</formula1>
     </dataValidation>
   </dataValidations>

--- a/assets/inventory/excel/רשימה 2.xlsx
+++ b/assets/inventory/excel/רשימה 2.xlsx
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="27" uniqueCount="20">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="31" uniqueCount="23">
   <si>
     <t>רשימת מכנסיים</t>
   </si>
@@ -92,6 +92,15 @@
   </si>
   <si>
     <t>m</t>
+  </si>
+  <si>
+    <t>#32</t>
+  </si>
+  <si>
+    <t>tong and country</t>
+  </si>
+  <si>
+    <t>xl</t>
   </si>
 </sst>
 </file>
@@ -631,7 +640,7 @@
         <v>8</v>
       </c>
       <c r="F4" s="21">
-        <v>250</v>
+        <v>150</v>
       </c>
       <c r="K4" s="15" t="s">
         <v>9</v>
@@ -704,12 +713,24 @@
       </c>
     </row>
     <row r="8" spans="1:11" ht="16.75" customHeight="1">
-      <c r="A8" s="8"/>
-      <c r="B8" s="5"/>
-      <c r="C8" s="11"/>
-      <c r="D8" s="17"/>
-      <c r="E8" s="20"/>
-      <c r="F8" s="21"/>
+      <c r="A8" s="8" t="s">
+        <v>20</v>
+      </c>
+      <c r="B8" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="C8" s="11" t="s">
+        <v>22</v>
+      </c>
+      <c r="D8" s="17">
+        <v>46218</v>
+      </c>
+      <c r="E8" s="20" t="s">
+        <v>8</v>
+      </c>
+      <c r="F8" s="21">
+        <v>150</v>
+      </c>
     </row>
     <row r="9" spans="1:11" ht="16.75" customHeight="1">
       <c r="A9" s="8"/>

--- a/assets/inventory/excel/רשימה 2.xlsx
+++ b/assets/inventory/excel/רשימה 2.xlsx
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="31" uniqueCount="23">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="56" uniqueCount="46">
   <si>
     <t>רשימת מכנסיים</t>
   </si>
@@ -101,6 +101,75 @@
   </si>
   <si>
     <t>xl</t>
+  </si>
+  <si>
+    <t>#33</t>
+  </si>
+  <si>
+    <t>#34</t>
+  </si>
+  <si>
+    <t>#35</t>
+  </si>
+  <si>
+    <t>#36</t>
+  </si>
+  <si>
+    <t>#37</t>
+  </si>
+  <si>
+    <t>#38</t>
+  </si>
+  <si>
+    <t>#39</t>
+  </si>
+  <si>
+    <t>#40</t>
+  </si>
+  <si>
+    <t>#41</t>
+  </si>
+  <si>
+    <t>#42</t>
+  </si>
+  <si>
+    <t>#43</t>
+  </si>
+  <si>
+    <t>#44</t>
+  </si>
+  <si>
+    <t>#45</t>
+  </si>
+  <si>
+    <t>#46</t>
+  </si>
+  <si>
+    <t>#47</t>
+  </si>
+  <si>
+    <t>#48</t>
+  </si>
+  <si>
+    <t>#49</t>
+  </si>
+  <si>
+    <t>#50</t>
+  </si>
+  <si>
+    <t>#51</t>
+  </si>
+  <si>
+    <t>#52</t>
+  </si>
+  <si>
+    <t>#53</t>
+  </si>
+  <si>
+    <t>#54</t>
+  </si>
+  <si>
+    <t>s</t>
   </si>
 </sst>
 </file>
@@ -162,14 +231,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="15">
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
+  <borders count="14">
     <border>
       <left/>
       <right/>
@@ -284,9 +346,9 @@
     </border>
   </borders>
   <cellStyleXfs count="1">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="11"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10"/>
   </cellStyleXfs>
-  <cellXfs count="27">
+  <cellXfs count="26">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -303,7 +365,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
@@ -312,47 +374,44 @@
     <xf numFmtId="49" fontId="0" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="1" fontId="0" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="1" fontId="0" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="1" fontId="0" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="14" fontId="4" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="1" fontId="0" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="14" fontId="4" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="3" fillId="4" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="3" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="3" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="3" fillId="4" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="3" fillId="4" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="3" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="14" fontId="3" fillId="4" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="3" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="3" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="3" fillId="4" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="3" fillId="4" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="3" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
@@ -582,24 +641,24 @@
     <col min="3" max="3" width="12" customWidth="1"/>
     <col min="4" max="4" width="15.5" customWidth="1"/>
     <col min="5" max="5" width="12.58203125" customWidth="1"/>
-    <col min="6" max="6" width="9.9140625" style="23" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="9.9140625" style="22" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="9.58203125" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="9.6640625" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="9.6640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:11" ht="24" customHeight="1">
-      <c r="A1" s="25" t="s">
+      <c r="A1" s="24" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="26"/>
-      <c r="C1" s="26"/>
+      <c r="B1" s="25"/>
+      <c r="C1" s="25"/>
     </row>
     <row r="2" spans="1:11" ht="15" customHeight="1" thickBot="1">
-      <c r="J2" s="13" t="s">
+      <c r="J2" s="12" t="s">
         <v>1</v>
       </c>
-      <c r="K2" s="14">
+      <c r="K2" s="13">
         <v>46217</v>
       </c>
     </row>
@@ -613,13 +672,13 @@
       <c r="C3" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="D3" s="16" t="s">
+      <c r="D3" s="15" t="s">
         <v>5</v>
       </c>
-      <c r="E3" s="24" t="s">
+      <c r="E3" s="23" t="s">
         <v>6</v>
       </c>
-      <c r="F3" s="24" t="s">
+      <c r="F3" s="23" t="s">
         <v>7</v>
       </c>
     </row>
@@ -630,19 +689,19 @@
       <c r="B4" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="C4" s="10" t="s">
+      <c r="C4" s="9" t="s">
         <v>13</v>
       </c>
-      <c r="D4" s="17">
+      <c r="D4" s="16">
         <v>46218</v>
       </c>
-      <c r="E4" s="20" t="s">
+      <c r="E4" s="19" t="s">
         <v>8</v>
       </c>
-      <c r="F4" s="21">
+      <c r="F4" s="20">
         <v>150</v>
       </c>
-      <c r="K4" s="15" t="s">
+      <c r="K4" s="14" t="s">
         <v>9</v>
       </c>
     </row>
@@ -653,16 +712,16 @@
       <c r="B5" s="5" t="s">
         <v>15</v>
       </c>
-      <c r="C5" s="11" t="s">
+      <c r="C5" s="10" t="s">
         <v>13</v>
       </c>
-      <c r="D5" s="18">
+      <c r="D5" s="17">
         <v>46218</v>
       </c>
-      <c r="E5" s="19" t="s">
+      <c r="E5" s="18" t="s">
         <v>8</v>
       </c>
-      <c r="F5" s="22">
+      <c r="F5" s="21">
         <v>150</v>
       </c>
       <c r="K5" t="s">
@@ -676,16 +735,16 @@
       <c r="B6" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="C6" s="11" t="s">
+      <c r="C6" s="10" t="s">
         <v>13</v>
       </c>
-      <c r="D6" s="17">
+      <c r="D6" s="16">
         <v>46218</v>
       </c>
-      <c r="E6" s="20" t="s">
+      <c r="E6" s="19" t="s">
         <v>8</v>
       </c>
-      <c r="F6" s="21">
+      <c r="F6" s="20">
         <v>150</v>
       </c>
       <c r="K6" t="s">
@@ -699,16 +758,16 @@
       <c r="B7" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="C7" s="11" t="s">
+      <c r="C7" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="D7" s="18">
+      <c r="D7" s="17">
         <v>46218</v>
       </c>
-      <c r="E7" s="19" t="s">
+      <c r="E7" s="18" t="s">
         <v>8</v>
       </c>
-      <c r="F7" s="22">
+      <c r="F7" s="21">
         <v>150</v>
       </c>
     </row>
@@ -719,194 +778,248 @@
       <c r="B8" s="5" t="s">
         <v>21</v>
       </c>
-      <c r="C8" s="11" t="s">
+      <c r="C8" s="10" t="s">
         <v>22</v>
       </c>
-      <c r="D8" s="17">
+      <c r="D8" s="16">
         <v>46218</v>
       </c>
-      <c r="E8" s="20" t="s">
+      <c r="E8" s="19" t="s">
         <v>8</v>
       </c>
-      <c r="F8" s="21">
+      <c r="F8" s="20">
         <v>150</v>
       </c>
     </row>
     <row r="9" spans="1:11" ht="16.75" customHeight="1">
-      <c r="A9" s="8"/>
-      <c r="B9" s="5"/>
-      <c r="C9" s="11"/>
-      <c r="D9" s="18"/>
-      <c r="E9" s="19"/>
-      <c r="F9" s="22"/>
+      <c r="A9" s="8" t="s">
+        <v>23</v>
+      </c>
+      <c r="B9" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="C9" s="10" t="s">
+        <v>45</v>
+      </c>
+      <c r="D9" s="17">
+        <v>46218</v>
+      </c>
+      <c r="E9" s="18" t="s">
+        <v>8</v>
+      </c>
+      <c r="F9" s="21">
+        <v>150</v>
+      </c>
     </row>
     <row r="10" spans="1:11" ht="16.75" customHeight="1">
-      <c r="A10" s="8"/>
+      <c r="A10" s="8" t="s">
+        <v>24</v>
+      </c>
       <c r="B10" s="5"/>
-      <c r="C10" s="11"/>
-      <c r="D10" s="17"/>
-      <c r="E10" s="20"/>
-      <c r="F10" s="21"/>
+      <c r="C10" s="10"/>
+      <c r="D10" s="16"/>
+      <c r="E10" s="19"/>
+      <c r="F10" s="20"/>
     </row>
     <row r="11" spans="1:11" ht="16.75" customHeight="1">
-      <c r="A11" s="8"/>
+      <c r="A11" s="8" t="s">
+        <v>25</v>
+      </c>
       <c r="B11" s="5"/>
-      <c r="C11" s="11"/>
-      <c r="D11" s="18"/>
-      <c r="E11" s="19"/>
-      <c r="F11" s="22"/>
+      <c r="C11" s="10"/>
+      <c r="D11" s="17"/>
+      <c r="E11" s="18"/>
+      <c r="F11" s="21"/>
     </row>
     <row r="12" spans="1:11" ht="16.75" customHeight="1">
-      <c r="A12" s="8"/>
+      <c r="A12" s="8" t="s">
+        <v>26</v>
+      </c>
       <c r="B12" s="5"/>
-      <c r="C12" s="11"/>
-      <c r="D12" s="17"/>
-      <c r="E12" s="20"/>
-      <c r="F12" s="21"/>
+      <c r="C12" s="10"/>
+      <c r="D12" s="16"/>
+      <c r="E12" s="19"/>
+      <c r="F12" s="20"/>
     </row>
     <row r="13" spans="1:11" ht="16.75" customHeight="1">
-      <c r="A13" s="8"/>
+      <c r="A13" s="8" t="s">
+        <v>27</v>
+      </c>
       <c r="B13" s="5"/>
-      <c r="C13" s="11"/>
-      <c r="D13" s="18"/>
-      <c r="E13" s="19"/>
-      <c r="F13" s="22"/>
+      <c r="C13" s="10"/>
+      <c r="D13" s="17"/>
+      <c r="E13" s="18"/>
+      <c r="F13" s="21"/>
     </row>
     <row r="14" spans="1:11" ht="16.75" customHeight="1">
-      <c r="A14" s="8"/>
+      <c r="A14" s="8" t="s">
+        <v>28</v>
+      </c>
       <c r="B14" s="5"/>
-      <c r="C14" s="11"/>
-      <c r="D14" s="17"/>
-      <c r="E14" s="20"/>
-      <c r="F14" s="21"/>
+      <c r="C14" s="10"/>
+      <c r="D14" s="16"/>
+      <c r="E14" s="19"/>
+      <c r="F14" s="20"/>
     </row>
     <row r="15" spans="1:11" ht="16.75" customHeight="1">
-      <c r="A15" s="8"/>
+      <c r="A15" s="8" t="s">
+        <v>29</v>
+      </c>
       <c r="B15" s="5"/>
-      <c r="C15" s="11"/>
-      <c r="D15" s="18"/>
-      <c r="E15" s="19"/>
-      <c r="F15" s="22"/>
+      <c r="C15" s="10"/>
+      <c r="D15" s="17"/>
+      <c r="E15" s="18"/>
+      <c r="F15" s="21"/>
     </row>
     <row r="16" spans="1:11" ht="16.75" customHeight="1">
-      <c r="A16" s="8"/>
+      <c r="A16" s="8" t="s">
+        <v>30</v>
+      </c>
       <c r="B16" s="5"/>
-      <c r="C16" s="11"/>
-      <c r="D16" s="17"/>
-      <c r="E16" s="20"/>
-      <c r="F16" s="21"/>
+      <c r="C16" s="10"/>
+      <c r="D16" s="16"/>
+      <c r="E16" s="19"/>
+      <c r="F16" s="20"/>
     </row>
     <row r="17" spans="1:6" ht="16.75" customHeight="1">
-      <c r="A17" s="8"/>
+      <c r="A17" s="8" t="s">
+        <v>31</v>
+      </c>
       <c r="B17" s="5"/>
-      <c r="C17" s="11"/>
-      <c r="D17" s="18"/>
-      <c r="E17" s="19"/>
-      <c r="F17" s="22"/>
+      <c r="C17" s="10"/>
+      <c r="D17" s="17"/>
+      <c r="E17" s="18"/>
+      <c r="F17" s="21"/>
     </row>
     <row r="18" spans="1:6" ht="16.75" customHeight="1">
-      <c r="A18" s="8"/>
+      <c r="A18" s="8" t="s">
+        <v>32</v>
+      </c>
       <c r="B18" s="5"/>
-      <c r="C18" s="11"/>
-      <c r="D18" s="17"/>
-      <c r="E18" s="20"/>
-      <c r="F18" s="21"/>
+      <c r="C18" s="10"/>
+      <c r="D18" s="16"/>
+      <c r="E18" s="19"/>
+      <c r="F18" s="20"/>
     </row>
     <row r="19" spans="1:6" ht="16.75" customHeight="1">
-      <c r="A19" s="8"/>
+      <c r="A19" s="8" t="s">
+        <v>33</v>
+      </c>
       <c r="B19" s="5"/>
-      <c r="C19" s="11"/>
-      <c r="D19" s="18"/>
-      <c r="E19" s="19"/>
-      <c r="F19" s="22"/>
+      <c r="C19" s="10"/>
+      <c r="D19" s="17"/>
+      <c r="E19" s="18"/>
+      <c r="F19" s="21"/>
     </row>
     <row r="20" spans="1:6" ht="16.75" customHeight="1">
-      <c r="A20" s="8"/>
+      <c r="A20" s="8" t="s">
+        <v>34</v>
+      </c>
       <c r="B20" s="5"/>
-      <c r="C20" s="11"/>
-      <c r="D20" s="17"/>
-      <c r="E20" s="20"/>
-      <c r="F20" s="21"/>
+      <c r="C20" s="10"/>
+      <c r="D20" s="16"/>
+      <c r="E20" s="19"/>
+      <c r="F20" s="20"/>
     </row>
     <row r="21" spans="1:6" ht="16.75" customHeight="1">
-      <c r="A21" s="8"/>
+      <c r="A21" s="8" t="s">
+        <v>35</v>
+      </c>
       <c r="B21" s="5"/>
-      <c r="C21" s="11"/>
-      <c r="D21" s="18"/>
-      <c r="E21" s="19"/>
-      <c r="F21" s="22"/>
+      <c r="C21" s="10"/>
+      <c r="D21" s="17"/>
+      <c r="E21" s="18"/>
+      <c r="F21" s="21"/>
     </row>
     <row r="22" spans="1:6" ht="16.75" customHeight="1">
-      <c r="A22" s="8"/>
+      <c r="A22" s="8" t="s">
+        <v>36</v>
+      </c>
       <c r="B22" s="5"/>
-      <c r="C22" s="11"/>
-      <c r="D22" s="17"/>
-      <c r="E22" s="20"/>
-      <c r="F22" s="21"/>
+      <c r="C22" s="10"/>
+      <c r="D22" s="16"/>
+      <c r="E22" s="19"/>
+      <c r="F22" s="20"/>
     </row>
     <row r="23" spans="1:6" ht="16.75" customHeight="1">
-      <c r="A23" s="8"/>
+      <c r="A23" s="8" t="s">
+        <v>37</v>
+      </c>
       <c r="B23" s="5"/>
-      <c r="C23" s="11"/>
-      <c r="D23" s="18"/>
-      <c r="E23" s="19"/>
-      <c r="F23" s="22"/>
+      <c r="C23" s="10"/>
+      <c r="D23" s="17"/>
+      <c r="E23" s="18"/>
+      <c r="F23" s="21"/>
     </row>
     <row r="24" spans="1:6" ht="16.75" customHeight="1">
-      <c r="A24" s="8"/>
+      <c r="A24" s="8" t="s">
+        <v>38</v>
+      </c>
       <c r="B24" s="5"/>
-      <c r="C24" s="11"/>
-      <c r="D24" s="17"/>
-      <c r="E24" s="20"/>
-      <c r="F24" s="21"/>
+      <c r="C24" s="10"/>
+      <c r="D24" s="16"/>
+      <c r="E24" s="19"/>
+      <c r="F24" s="20"/>
     </row>
     <row r="25" spans="1:6" ht="16.75" customHeight="1">
-      <c r="A25" s="8"/>
+      <c r="A25" s="8" t="s">
+        <v>39</v>
+      </c>
       <c r="B25" s="5"/>
-      <c r="C25" s="11"/>
-      <c r="D25" s="18"/>
-      <c r="E25" s="19"/>
-      <c r="F25" s="22"/>
+      <c r="C25" s="10"/>
+      <c r="D25" s="17"/>
+      <c r="E25" s="18"/>
+      <c r="F25" s="21"/>
     </row>
     <row r="26" spans="1:6" ht="16.75" customHeight="1">
-      <c r="A26" s="8"/>
+      <c r="A26" s="8" t="s">
+        <v>40</v>
+      </c>
       <c r="B26" s="5"/>
-      <c r="C26" s="11"/>
-      <c r="D26" s="17"/>
-      <c r="E26" s="20"/>
-      <c r="F26" s="21"/>
+      <c r="C26" s="10"/>
+      <c r="D26" s="16"/>
+      <c r="E26" s="19"/>
+      <c r="F26" s="20"/>
     </row>
     <row r="27" spans="1:6" ht="16.75" customHeight="1">
-      <c r="A27" s="8"/>
+      <c r="A27" s="8" t="s">
+        <v>41</v>
+      </c>
       <c r="B27" s="5"/>
-      <c r="C27" s="11"/>
-      <c r="D27" s="18"/>
-      <c r="E27" s="19"/>
-      <c r="F27" s="22"/>
+      <c r="C27" s="10"/>
+      <c r="D27" s="17"/>
+      <c r="E27" s="18"/>
+      <c r="F27" s="21"/>
     </row>
     <row r="28" spans="1:6" ht="16.75" customHeight="1">
-      <c r="A28" s="8"/>
+      <c r="A28" s="8" t="s">
+        <v>42</v>
+      </c>
       <c r="B28" s="5"/>
-      <c r="C28" s="11"/>
-      <c r="D28" s="17"/>
-      <c r="E28" s="20"/>
-      <c r="F28" s="21"/>
+      <c r="C28" s="10"/>
+      <c r="D28" s="16"/>
+      <c r="E28" s="19"/>
+      <c r="F28" s="20"/>
     </row>
     <row r="29" spans="1:6" ht="16.75" customHeight="1">
-      <c r="A29" s="8"/>
+      <c r="A29" s="8" t="s">
+        <v>43</v>
+      </c>
       <c r="B29" s="5"/>
-      <c r="C29" s="11"/>
-      <c r="D29" s="18"/>
-      <c r="E29" s="19"/>
-      <c r="F29" s="22"/>
+      <c r="C29" s="10"/>
+      <c r="D29" s="17"/>
+      <c r="E29" s="18"/>
+      <c r="F29" s="21"/>
     </row>
     <row r="30" spans="1:6" ht="16.75" customHeight="1">
-      <c r="A30" s="9"/>
+      <c r="A30" s="8" t="s">
+        <v>44</v>
+      </c>
       <c r="B30" s="6"/>
-      <c r="C30" s="12"/>
-      <c r="D30" s="17"/>
-      <c r="E30" s="20"/>
-      <c r="F30" s="21"/>
+      <c r="C30" s="11"/>
+      <c r="D30" s="16"/>
+      <c r="E30" s="19"/>
+      <c r="F30" s="20"/>
     </row>
   </sheetData>
   <mergeCells count="1">

--- a/assets/inventory/excel/רשימה 2.xlsx
+++ b/assets/inventory/excel/רשימה 2.xlsx
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="56" uniqueCount="46">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="71" uniqueCount="46">
   <si>
     <t>רשימת מכנסיים</t>
   </si>
@@ -693,7 +693,7 @@
         <v>13</v>
       </c>
       <c r="D4" s="16">
-        <v>46218</v>
+        <v>46217</v>
       </c>
       <c r="E4" s="19" t="s">
         <v>8</v>
@@ -715,14 +715,14 @@
       <c r="C5" s="10" t="s">
         <v>13</v>
       </c>
-      <c r="D5" s="17">
-        <v>46218</v>
+      <c r="D5" s="16">
+        <v>46217</v>
       </c>
       <c r="E5" s="18" t="s">
         <v>8</v>
       </c>
       <c r="F5" s="21">
-        <v>150</v>
+        <v>140</v>
       </c>
       <c r="K5" t="s">
         <v>10</v>
@@ -739,13 +739,13 @@
         <v>13</v>
       </c>
       <c r="D6" s="16">
-        <v>46218</v>
+        <v>46217</v>
       </c>
       <c r="E6" s="19" t="s">
         <v>8</v>
       </c>
       <c r="F6" s="20">
-        <v>150</v>
+        <v>140</v>
       </c>
       <c r="K6" t="s">
         <v>8</v>
@@ -761,8 +761,8 @@
       <c r="C7" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="D7" s="17">
-        <v>46218</v>
+      <c r="D7" s="16">
+        <v>46217</v>
       </c>
       <c r="E7" s="18" t="s">
         <v>8</v>
@@ -782,13 +782,13 @@
         <v>22</v>
       </c>
       <c r="D8" s="16">
-        <v>46218</v>
+        <v>46217</v>
       </c>
       <c r="E8" s="19" t="s">
         <v>8</v>
       </c>
       <c r="F8" s="20">
-        <v>150</v>
+        <v>125</v>
       </c>
     </row>
     <row r="9" spans="1:11" ht="16.75" customHeight="1">
@@ -801,8 +801,8 @@
       <c r="C9" s="10" t="s">
         <v>45</v>
       </c>
-      <c r="D9" s="17">
-        <v>46218</v>
+      <c r="D9" s="16">
+        <v>46217</v>
       </c>
       <c r="E9" s="18" t="s">
         <v>8</v>
@@ -815,51 +815,101 @@
       <c r="A10" s="8" t="s">
         <v>24</v>
       </c>
-      <c r="B10" s="5"/>
-      <c r="C10" s="10"/>
-      <c r="D10" s="16"/>
-      <c r="E10" s="19"/>
-      <c r="F10" s="20"/>
+      <c r="B10" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="C10" s="10" t="s">
+        <v>19</v>
+      </c>
+      <c r="D10" s="16">
+        <v>46217</v>
+      </c>
+      <c r="E10" s="19" t="s">
+        <v>8</v>
+      </c>
+      <c r="F10" s="20">
+        <v>125</v>
+      </c>
     </row>
     <row r="11" spans="1:11" ht="16.75" customHeight="1">
       <c r="A11" s="8" t="s">
         <v>25</v>
       </c>
-      <c r="B11" s="5"/>
-      <c r="C11" s="10"/>
-      <c r="D11" s="17"/>
-      <c r="E11" s="18"/>
-      <c r="F11" s="21"/>
+      <c r="B11" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="C11" s="10" t="s">
+        <v>45</v>
+      </c>
+      <c r="D11" s="17">
+        <v>46217</v>
+      </c>
+      <c r="E11" s="18" t="s">
+        <v>8</v>
+      </c>
+      <c r="F11" s="21">
+        <v>150</v>
+      </c>
     </row>
     <row r="12" spans="1:11" ht="16.75" customHeight="1">
       <c r="A12" s="8" t="s">
         <v>26</v>
       </c>
-      <c r="B12" s="5"/>
-      <c r="C12" s="10"/>
-      <c r="D12" s="16"/>
-      <c r="E12" s="19"/>
-      <c r="F12" s="20"/>
+      <c r="B12" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="C12" s="10" t="s">
+        <v>13</v>
+      </c>
+      <c r="D12" s="16">
+        <v>46217</v>
+      </c>
+      <c r="E12" s="19" t="s">
+        <v>8</v>
+      </c>
+      <c r="F12" s="20">
+        <v>125</v>
+      </c>
     </row>
     <row r="13" spans="1:11" ht="16.75" customHeight="1">
       <c r="A13" s="8" t="s">
         <v>27</v>
       </c>
-      <c r="B13" s="5"/>
-      <c r="C13" s="10"/>
-      <c r="D13" s="17"/>
-      <c r="E13" s="18"/>
-      <c r="F13" s="21"/>
+      <c r="B13" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="C13" s="10" t="s">
+        <v>13</v>
+      </c>
+      <c r="D13" s="17">
+        <v>46217</v>
+      </c>
+      <c r="E13" s="18" t="s">
+        <v>8</v>
+      </c>
+      <c r="F13" s="21">
+        <v>130</v>
+      </c>
     </row>
     <row r="14" spans="1:11" ht="16.75" customHeight="1">
       <c r="A14" s="8" t="s">
         <v>28</v>
       </c>
-      <c r="B14" s="5"/>
-      <c r="C14" s="10"/>
-      <c r="D14" s="16"/>
-      <c r="E14" s="19"/>
-      <c r="F14" s="20"/>
+      <c r="B14" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="C14" s="10" t="s">
+        <v>13</v>
+      </c>
+      <c r="D14" s="16">
+        <v>46217</v>
+      </c>
+      <c r="E14" s="19" t="s">
+        <v>8</v>
+      </c>
+      <c r="F14" s="20">
+        <v>140</v>
+      </c>
     </row>
     <row r="15" spans="1:11" ht="16.75" customHeight="1">
       <c r="A15" s="8" t="s">

--- a/assets/inventory/excel/רשימה 2.xlsx
+++ b/assets/inventory/excel/רשימה 2.xlsx
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="71" uniqueCount="46">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="84" uniqueCount="49">
   <si>
     <t>רשימת מכנסיים</t>
   </si>
@@ -170,6 +170,15 @@
   </si>
   <si>
     <t>s</t>
+  </si>
+  <si>
+    <t>billabong</t>
+  </si>
+  <si>
+    <t>fire</t>
+  </si>
+  <si>
+    <t>oniell</t>
   </si>
 </sst>
 </file>
@@ -915,61 +924,121 @@
       <c r="A15" s="8" t="s">
         <v>29</v>
       </c>
-      <c r="B15" s="5"/>
-      <c r="C15" s="10"/>
-      <c r="D15" s="17"/>
-      <c r="E15" s="18"/>
-      <c r="F15" s="21"/>
+      <c r="B15" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="C15" s="10">
+        <v>32</v>
+      </c>
+      <c r="D15" s="17">
+        <v>46217</v>
+      </c>
+      <c r="E15" s="18" t="s">
+        <v>8</v>
+      </c>
+      <c r="F15" s="21">
+        <v>250</v>
+      </c>
     </row>
     <row r="16" spans="1:11" ht="16.75" customHeight="1">
       <c r="A16" s="8" t="s">
         <v>30</v>
       </c>
-      <c r="B16" s="5"/>
-      <c r="C16" s="10"/>
-      <c r="D16" s="16"/>
-      <c r="E16" s="19"/>
-      <c r="F16" s="20"/>
+      <c r="B16" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="C16" s="10">
+        <v>34</v>
+      </c>
+      <c r="D16" s="16">
+        <v>46217</v>
+      </c>
+      <c r="E16" s="19" t="s">
+        <v>8</v>
+      </c>
+      <c r="F16" s="20">
+        <v>250</v>
+      </c>
     </row>
     <row r="17" spans="1:6" ht="16.75" customHeight="1">
       <c r="A17" s="8" t="s">
         <v>31</v>
       </c>
-      <c r="B17" s="5"/>
-      <c r="C17" s="10"/>
-      <c r="D17" s="17"/>
-      <c r="E17" s="18"/>
-      <c r="F17" s="21"/>
+      <c r="B17" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="C17" s="10">
+        <v>36</v>
+      </c>
+      <c r="D17" s="17">
+        <v>46217</v>
+      </c>
+      <c r="E17" s="18" t="s">
+        <v>8</v>
+      </c>
+      <c r="F17" s="21">
+        <v>230</v>
+      </c>
     </row>
     <row r="18" spans="1:6" ht="16.75" customHeight="1">
       <c r="A18" s="8" t="s">
         <v>32</v>
       </c>
-      <c r="B18" s="5"/>
-      <c r="C18" s="10"/>
-      <c r="D18" s="16"/>
-      <c r="E18" s="19"/>
-      <c r="F18" s="20"/>
+      <c r="B18" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="C18" s="10">
+        <v>31</v>
+      </c>
+      <c r="D18" s="16">
+        <v>46217</v>
+      </c>
+      <c r="E18" s="19" t="s">
+        <v>8</v>
+      </c>
+      <c r="F18" s="20">
+        <v>260</v>
+      </c>
     </row>
     <row r="19" spans="1:6" ht="16.75" customHeight="1">
       <c r="A19" s="8" t="s">
         <v>33</v>
       </c>
-      <c r="B19" s="5"/>
-      <c r="C19" s="10"/>
-      <c r="D19" s="17"/>
-      <c r="E19" s="18"/>
-      <c r="F19" s="21"/>
+      <c r="B19" s="5" t="s">
+        <v>47</v>
+      </c>
+      <c r="C19" s="10" t="s">
+        <v>13</v>
+      </c>
+      <c r="D19" s="17">
+        <v>46217</v>
+      </c>
+      <c r="E19" s="18" t="s">
+        <v>8</v>
+      </c>
+      <c r="F19" s="21">
+        <v>230</v>
+      </c>
     </row>
     <row r="20" spans="1:6" ht="16.75" customHeight="1">
       <c r="A20" s="8" t="s">
         <v>34</v>
       </c>
-      <c r="B20" s="5"/>
-      <c r="C20" s="10"/>
-      <c r="D20" s="16"/>
-      <c r="E20" s="19"/>
-      <c r="F20" s="20"/>
+      <c r="B20" s="5" t="s">
+        <v>48</v>
+      </c>
+      <c r="C20" s="10">
+        <v>36</v>
+      </c>
+      <c r="D20" s="16">
+        <v>46217</v>
+      </c>
+      <c r="E20" s="19" t="s">
+        <v>8</v>
+      </c>
+      <c r="F20" s="20">
+        <v>260</v>
+      </c>
     </row>
     <row r="21" spans="1:6" ht="16.75" customHeight="1">
       <c r="A21" s="8" t="s">

--- a/assets/inventory/excel/רשימה 2.xlsx
+++ b/assets/inventory/excel/רשימה 2.xlsx
@@ -728,7 +728,7 @@
         <v>46217</v>
       </c>
       <c r="E5" s="18" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="F5" s="21">
         <v>140</v>
@@ -874,7 +874,7 @@
         <v>46217</v>
       </c>
       <c r="E12" s="19" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="F12" s="20">
         <v>125</v>

--- a/assets/inventory/excel/רשימה 2.xlsx
+++ b/assets/inventory/excel/רשימה 2.xlsx
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="84" uniqueCount="49">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="97" uniqueCount="51">
   <si>
     <t>רשימת מכנסיים</t>
   </si>
@@ -179,6 +179,12 @@
   </si>
   <si>
     <t>oniell</t>
+  </si>
+  <si>
+    <t>blue</t>
+  </si>
+  <si>
+    <t>flowers</t>
   </si>
 </sst>
 </file>
@@ -1044,61 +1050,121 @@
       <c r="A21" s="8" t="s">
         <v>35</v>
       </c>
-      <c r="B21" s="5"/>
-      <c r="C21" s="10"/>
-      <c r="D21" s="17"/>
-      <c r="E21" s="18"/>
-      <c r="F21" s="21"/>
+      <c r="B21" s="5" t="s">
+        <v>49</v>
+      </c>
+      <c r="C21" s="10">
+        <v>29</v>
+      </c>
+      <c r="D21" s="17">
+        <v>46219</v>
+      </c>
+      <c r="E21" s="18" t="s">
+        <v>8</v>
+      </c>
+      <c r="F21" s="21">
+        <v>230</v>
+      </c>
     </row>
     <row r="22" spans="1:6" ht="16.75" customHeight="1">
       <c r="A22" s="8" t="s">
         <v>36</v>
       </c>
-      <c r="B22" s="5"/>
-      <c r="C22" s="10"/>
-      <c r="D22" s="16"/>
-      <c r="E22" s="19"/>
-      <c r="F22" s="20"/>
+      <c r="B22" s="5" t="s">
+        <v>50</v>
+      </c>
+      <c r="C22" s="10">
+        <v>32</v>
+      </c>
+      <c r="D22" s="16">
+        <v>46219</v>
+      </c>
+      <c r="E22" s="19" t="s">
+        <v>8</v>
+      </c>
+      <c r="F22" s="20">
+        <v>230</v>
+      </c>
     </row>
     <row r="23" spans="1:6" ht="16.75" customHeight="1">
       <c r="A23" s="8" t="s">
         <v>37</v>
       </c>
-      <c r="B23" s="5"/>
-      <c r="C23" s="10"/>
-      <c r="D23" s="17"/>
-      <c r="E23" s="18"/>
-      <c r="F23" s="21"/>
+      <c r="B23" s="5" t="s">
+        <v>50</v>
+      </c>
+      <c r="C23" s="10">
+        <v>36</v>
+      </c>
+      <c r="D23" s="17">
+        <v>46219</v>
+      </c>
+      <c r="E23" s="18" t="s">
+        <v>8</v>
+      </c>
+      <c r="F23" s="21">
+        <v>200</v>
+      </c>
     </row>
     <row r="24" spans="1:6" ht="16.75" customHeight="1">
       <c r="A24" s="8" t="s">
         <v>38</v>
       </c>
-      <c r="B24" s="5"/>
-      <c r="C24" s="10"/>
-      <c r="D24" s="16"/>
-      <c r="E24" s="19"/>
-      <c r="F24" s="20"/>
+      <c r="B24" s="5" t="s">
+        <v>48</v>
+      </c>
+      <c r="C24" s="10">
+        <v>32</v>
+      </c>
+      <c r="D24" s="16">
+        <v>46219</v>
+      </c>
+      <c r="E24" s="19" t="s">
+        <v>8</v>
+      </c>
+      <c r="F24" s="20">
+        <v>230</v>
+      </c>
     </row>
     <row r="25" spans="1:6" ht="16.75" customHeight="1">
       <c r="A25" s="8" t="s">
         <v>39</v>
       </c>
-      <c r="B25" s="5"/>
-      <c r="C25" s="10"/>
-      <c r="D25" s="17"/>
-      <c r="E25" s="18"/>
-      <c r="F25" s="21"/>
+      <c r="B25" s="5" t="s">
+        <v>47</v>
+      </c>
+      <c r="C25" s="10">
+        <v>34</v>
+      </c>
+      <c r="D25" s="17">
+        <v>46219</v>
+      </c>
+      <c r="E25" s="18" t="s">
+        <v>8</v>
+      </c>
+      <c r="F25" s="21">
+        <v>250</v>
+      </c>
     </row>
     <row r="26" spans="1:6" ht="16.75" customHeight="1">
       <c r="A26" s="8" t="s">
         <v>40</v>
       </c>
-      <c r="B26" s="5"/>
-      <c r="C26" s="10"/>
-      <c r="D26" s="16"/>
-      <c r="E26" s="19"/>
-      <c r="F26" s="20"/>
+      <c r="B26" s="5" t="s">
+        <v>50</v>
+      </c>
+      <c r="C26" s="10" t="s">
+        <v>13</v>
+      </c>
+      <c r="D26" s="16">
+        <v>46219</v>
+      </c>
+      <c r="E26" s="19" t="s">
+        <v>8</v>
+      </c>
+      <c r="F26" s="20">
+        <v>200</v>
+      </c>
     </row>
     <row r="27" spans="1:6" ht="16.75" customHeight="1">
       <c r="A27" s="8" t="s">
@@ -1106,7 +1172,9 @@
       </c>
       <c r="B27" s="5"/>
       <c r="C27" s="10"/>
-      <c r="D27" s="17"/>
+      <c r="D27" s="17">
+        <v>46219</v>
+      </c>
       <c r="E27" s="18"/>
       <c r="F27" s="21"/>
     </row>
@@ -1116,7 +1184,9 @@
       </c>
       <c r="B28" s="5"/>
       <c r="C28" s="10"/>
-      <c r="D28" s="16"/>
+      <c r="D28" s="16">
+        <v>46219</v>
+      </c>
       <c r="E28" s="19"/>
       <c r="F28" s="20"/>
     </row>
@@ -1126,7 +1196,9 @@
       </c>
       <c r="B29" s="5"/>
       <c r="C29" s="10"/>
-      <c r="D29" s="17"/>
+      <c r="D29" s="17">
+        <v>46219</v>
+      </c>
       <c r="E29" s="18"/>
       <c r="F29" s="21"/>
     </row>
@@ -1136,7 +1208,9 @@
       </c>
       <c r="B30" s="6"/>
       <c r="C30" s="11"/>
-      <c r="D30" s="16"/>
+      <c r="D30" s="16">
+        <v>46219</v>
+      </c>
       <c r="E30" s="19"/>
       <c r="F30" s="20"/>
     </row>

--- a/assets/inventory/excel/רשימה 2.xlsx
+++ b/assets/inventory/excel/רשימה 2.xlsx
@@ -900,7 +900,7 @@
         <v>46217</v>
       </c>
       <c r="E13" s="18" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="F13" s="21">
         <v>130</v>
@@ -960,7 +960,7 @@
         <v>46217</v>
       </c>
       <c r="E16" s="19" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="F16" s="20">
         <v>250</v>

--- a/assets/inventory/excel/רשימה 2.xlsx
+++ b/assets/inventory/excel/רשימה 2.xlsx
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="97" uniqueCount="51">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="139" uniqueCount="69">
   <si>
     <t>רשימת מכנסיים</t>
   </si>
@@ -185,6 +185,60 @@
   </si>
   <si>
     <t>flowers</t>
+  </si>
+  <si>
+    <t>Andy irons</t>
+  </si>
+  <si>
+    <t>#55</t>
+  </si>
+  <si>
+    <t>#56</t>
+  </si>
+  <si>
+    <t>#57</t>
+  </si>
+  <si>
+    <t>#58</t>
+  </si>
+  <si>
+    <t>#59</t>
+  </si>
+  <si>
+    <t>#60</t>
+  </si>
+  <si>
+    <t>#61</t>
+  </si>
+  <si>
+    <t>#62</t>
+  </si>
+  <si>
+    <t>#63</t>
+  </si>
+  <si>
+    <t>#64</t>
+  </si>
+  <si>
+    <t>#65</t>
+  </si>
+  <si>
+    <t>PINK</t>
+  </si>
+  <si>
+    <t xml:space="preserve">              BILLABONG</t>
+  </si>
+  <si>
+    <t xml:space="preserve">               billabong</t>
+  </si>
+  <si>
+    <t xml:space="preserve">                  billabong</t>
+  </si>
+  <si>
+    <t>GRAY</t>
+  </si>
+  <si>
+    <t>MILITARY</t>
   </si>
 </sst>
 </file>
@@ -246,7 +300,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="14">
+  <borders count="15">
     <border>
       <left/>
       <right/>
@@ -359,11 +413,20 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4" tint="0.39997558519241921"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="10"/>
   </cellStyleXfs>
-  <cellXfs count="26">
+  <cellXfs count="28">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -430,6 +493,10 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1"/>
+    <xf numFmtId="14" fontId="3" fillId="4" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -486,7 +553,7 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="PantsTable" displayName="PantsTable" ref="A3:D30">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="PantsTable" displayName="PantsTable" ref="A3:D41">
   <tableColumns count="4">
     <tableColumn id="1" name="מספר מכנס"/>
     <tableColumn id="2" name="שם מכנס"/>
@@ -648,7 +715,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:K30"/>
+  <dimension ref="A1:K41"/>
   <sheetFormatPr defaultRowHeight="14"/>
   <cols>
     <col min="1" max="1" width="15" customWidth="1"/>
@@ -1170,56 +1237,318 @@
       <c r="A27" s="8" t="s">
         <v>41</v>
       </c>
-      <c r="B27" s="5"/>
-      <c r="C27" s="10"/>
+      <c r="B27" s="5" t="s">
+        <v>51</v>
+      </c>
+      <c r="C27" s="10">
+        <v>36</v>
+      </c>
       <c r="D27" s="17">
         <v>46219</v>
       </c>
-      <c r="E27" s="18"/>
-      <c r="F27" s="21"/>
+      <c r="E27" s="18" t="s">
+        <v>8</v>
+      </c>
+      <c r="F27" s="21">
+        <v>330</v>
+      </c>
     </row>
     <row r="28" spans="1:6" ht="16.75" customHeight="1">
       <c r="A28" s="8" t="s">
         <v>42</v>
       </c>
-      <c r="B28" s="5"/>
-      <c r="C28" s="10"/>
+      <c r="B28" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="C28" s="10">
+        <v>32</v>
+      </c>
       <c r="D28" s="16">
         <v>46219</v>
       </c>
-      <c r="E28" s="19"/>
-      <c r="F28" s="20"/>
+      <c r="E28" s="19" t="s">
+        <v>8</v>
+      </c>
+      <c r="F28" s="20">
+        <v>270</v>
+      </c>
     </row>
     <row r="29" spans="1:6" ht="16.75" customHeight="1">
       <c r="A29" s="8" t="s">
         <v>43</v>
       </c>
-      <c r="B29" s="5"/>
-      <c r="C29" s="10"/>
+      <c r="B29" s="5" t="s">
+        <v>51</v>
+      </c>
+      <c r="C29" s="10">
+        <v>31</v>
+      </c>
       <c r="D29" s="17">
         <v>46219</v>
       </c>
-      <c r="E29" s="18"/>
-      <c r="F29" s="21"/>
+      <c r="E29" s="18" t="s">
+        <v>8</v>
+      </c>
+      <c r="F29" s="21">
+        <v>330</v>
+      </c>
     </row>
     <row r="30" spans="1:6" ht="16.75" customHeight="1">
       <c r="A30" s="8" t="s">
         <v>44</v>
       </c>
-      <c r="B30" s="6"/>
-      <c r="C30" s="11"/>
+      <c r="B30" s="6" t="s">
+        <v>63</v>
+      </c>
+      <c r="C30" s="11">
+        <v>34</v>
+      </c>
       <c r="D30" s="16">
         <v>46219</v>
       </c>
-      <c r="E30" s="19"/>
-      <c r="F30" s="20"/>
+      <c r="E30" s="19" t="s">
+        <v>8</v>
+      </c>
+      <c r="F30" s="20">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="31" spans="1:6">
+      <c r="A31" s="26" t="s">
+        <v>52</v>
+      </c>
+      <c r="B31" s="26" t="s">
+        <v>64</v>
+      </c>
+      <c r="C31" s="26">
+        <v>32</v>
+      </c>
+      <c r="D31" s="27">
+        <v>46217</v>
+      </c>
+      <c r="E31" s="19" t="s">
+        <v>8</v>
+      </c>
+      <c r="F31" s="22">
+        <v>270</v>
+      </c>
+    </row>
+    <row r="32" spans="1:6">
+      <c r="A32" s="26" t="s">
+        <v>53</v>
+      </c>
+      <c r="B32" s="26" t="s">
+        <v>65</v>
+      </c>
+      <c r="C32" s="26">
+        <v>38</v>
+      </c>
+      <c r="D32" s="27">
+        <f>$K$2</f>
+        <v>46217</v>
+      </c>
+      <c r="E32" s="19" t="s">
+        <v>8</v>
+      </c>
+      <c r="F32" s="22">
+        <v>270</v>
+      </c>
+    </row>
+    <row r="33" spans="1:6">
+      <c r="A33" s="26" t="s">
+        <v>54</v>
+      </c>
+      <c r="B33" s="26" t="s">
+        <v>66</v>
+      </c>
+      <c r="C33" s="26">
+        <v>30</v>
+      </c>
+      <c r="D33" s="27">
+        <f>$K$2</f>
+        <v>46217</v>
+      </c>
+      <c r="E33" s="19" t="s">
+        <v>8</v>
+      </c>
+      <c r="F33" s="22">
+        <v>250</v>
+      </c>
+    </row>
+    <row r="34" spans="1:6">
+      <c r="A34" s="26" t="s">
+        <v>55</v>
+      </c>
+      <c r="B34" s="26" t="s">
+        <v>48</v>
+      </c>
+      <c r="C34" s="26">
+        <v>30</v>
+      </c>
+      <c r="D34" s="27">
+        <f>$K$2</f>
+        <v>46217</v>
+      </c>
+      <c r="E34" s="19" t="s">
+        <v>8</v>
+      </c>
+      <c r="F34" s="22">
+        <v>250</v>
+      </c>
+    </row>
+    <row r="35" spans="1:6">
+      <c r="A35" s="26" t="s">
+        <v>56</v>
+      </c>
+      <c r="B35" s="26" t="s">
+        <v>67</v>
+      </c>
+      <c r="C35" s="26">
+        <v>34</v>
+      </c>
+      <c r="D35" s="27">
+        <f>$K$2</f>
+        <v>46217</v>
+      </c>
+      <c r="E35" s="19" t="s">
+        <v>8</v>
+      </c>
+      <c r="F35" s="22">
+        <v>250</v>
+      </c>
+    </row>
+    <row r="36" spans="1:6">
+      <c r="A36" s="26" t="s">
+        <v>57</v>
+      </c>
+      <c r="B36" s="26" t="s">
+        <v>68</v>
+      </c>
+      <c r="C36" s="26" t="s">
+        <v>13</v>
+      </c>
+      <c r="D36" s="27">
+        <f>$K$2</f>
+        <v>46217</v>
+      </c>
+      <c r="E36" s="19" t="s">
+        <v>8</v>
+      </c>
+      <c r="F36" s="22">
+        <v>270</v>
+      </c>
+    </row>
+    <row r="37" spans="1:6">
+      <c r="A37" s="26" t="s">
+        <v>58</v>
+      </c>
+      <c r="B37" s="26" t="s">
+        <v>48</v>
+      </c>
+      <c r="C37" s="26">
+        <v>32</v>
+      </c>
+      <c r="D37" s="27">
+        <f>$K$2</f>
+        <v>46217</v>
+      </c>
+      <c r="E37" s="19" t="s">
+        <v>8</v>
+      </c>
+      <c r="F37" s="22">
+        <v>270</v>
+      </c>
+    </row>
+    <row r="38" spans="1:6">
+      <c r="A38" s="26" t="s">
+        <v>59</v>
+      </c>
+      <c r="B38" s="26" t="s">
+        <v>48</v>
+      </c>
+      <c r="C38" s="26">
+        <v>34</v>
+      </c>
+      <c r="D38" s="27">
+        <f>$K$2</f>
+        <v>46217</v>
+      </c>
+      <c r="E38" s="19" t="s">
+        <v>8</v>
+      </c>
+      <c r="F38" s="22">
+        <v>270</v>
+      </c>
+    </row>
+    <row r="39" spans="1:6">
+      <c r="A39" s="26" t="s">
+        <v>60</v>
+      </c>
+      <c r="B39" s="26" t="s">
+        <v>46</v>
+      </c>
+      <c r="C39" s="26">
+        <v>38</v>
+      </c>
+      <c r="D39" s="27">
+        <f>$K$2</f>
+        <v>46217</v>
+      </c>
+      <c r="E39" s="19" t="s">
+        <v>8</v>
+      </c>
+      <c r="F39" s="22">
+        <v>270</v>
+      </c>
+    </row>
+    <row r="40" spans="1:6">
+      <c r="A40" s="26" t="s">
+        <v>61</v>
+      </c>
+      <c r="B40" s="26" t="s">
+        <v>46</v>
+      </c>
+      <c r="C40" s="26">
+        <v>34</v>
+      </c>
+      <c r="D40" s="27">
+        <f>$K$2</f>
+        <v>46217</v>
+      </c>
+      <c r="E40" s="19" t="s">
+        <v>8</v>
+      </c>
+      <c r="F40" s="22">
+        <v>270</v>
+      </c>
+    </row>
+    <row r="41" spans="1:6">
+      <c r="A41" s="26" t="s">
+        <v>62</v>
+      </c>
+      <c r="B41" s="26" t="s">
+        <v>46</v>
+      </c>
+      <c r="C41" s="26">
+        <v>29</v>
+      </c>
+      <c r="D41" s="27">
+        <f>$K$2</f>
+        <v>46217</v>
+      </c>
+      <c r="E41" s="19" t="s">
+        <v>8</v>
+      </c>
+      <c r="F41" s="22">
+        <v>230</v>
+      </c>
     </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A1:C1"/>
   </mergeCells>
   <dataValidations count="1">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E4:E30">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E4:E41">
       <formula1>$K$5:$K$6</formula1>
     </dataValidation>
   </dataValidations>

--- a/assets/inventory/excel/רשימה 2.xlsx
+++ b/assets/inventory/excel/רשימה 2.xlsx
@@ -1324,7 +1324,7 @@
         <v>32</v>
       </c>
       <c r="D31" s="27">
-        <v>46217</v>
+        <v>46219</v>
       </c>
       <c r="E31" s="19" t="s">
         <v>8</v>
@@ -1344,8 +1344,7 @@
         <v>38</v>
       </c>
       <c r="D32" s="27">
-        <f>$K$2</f>
-        <v>46217</v>
+        <v>46219</v>
       </c>
       <c r="E32" s="19" t="s">
         <v>8</v>
@@ -1365,8 +1364,7 @@
         <v>30</v>
       </c>
       <c r="D33" s="27">
-        <f>$K$2</f>
-        <v>46217</v>
+        <v>46219</v>
       </c>
       <c r="E33" s="19" t="s">
         <v>8</v>
@@ -1386,8 +1384,7 @@
         <v>30</v>
       </c>
       <c r="D34" s="27">
-        <f>$K$2</f>
-        <v>46217</v>
+        <v>46219</v>
       </c>
       <c r="E34" s="19" t="s">
         <v>8</v>
@@ -1407,8 +1404,7 @@
         <v>34</v>
       </c>
       <c r="D35" s="27">
-        <f>$K$2</f>
-        <v>46217</v>
+        <v>46219</v>
       </c>
       <c r="E35" s="19" t="s">
         <v>8</v>
@@ -1428,8 +1424,7 @@
         <v>13</v>
       </c>
       <c r="D36" s="27">
-        <f>$K$2</f>
-        <v>46217</v>
+        <v>46219</v>
       </c>
       <c r="E36" s="19" t="s">
         <v>8</v>
@@ -1449,8 +1444,7 @@
         <v>32</v>
       </c>
       <c r="D37" s="27">
-        <f>$K$2</f>
-        <v>46217</v>
+        <v>46219</v>
       </c>
       <c r="E37" s="19" t="s">
         <v>8</v>
@@ -1470,8 +1464,7 @@
         <v>34</v>
       </c>
       <c r="D38" s="27">
-        <f>$K$2</f>
-        <v>46217</v>
+        <v>46219</v>
       </c>
       <c r="E38" s="19" t="s">
         <v>8</v>
@@ -1491,8 +1484,7 @@
         <v>38</v>
       </c>
       <c r="D39" s="27">
-        <f>$K$2</f>
-        <v>46217</v>
+        <v>46219</v>
       </c>
       <c r="E39" s="19" t="s">
         <v>8</v>
@@ -1512,8 +1504,7 @@
         <v>34</v>
       </c>
       <c r="D40" s="27">
-        <f>$K$2</f>
-        <v>46217</v>
+        <v>46219</v>
       </c>
       <c r="E40" s="19" t="s">
         <v>8</v>
@@ -1533,8 +1524,7 @@
         <v>29</v>
       </c>
       <c r="D41" s="27">
-        <f>$K$2</f>
-        <v>46217</v>
+        <v>46219</v>
       </c>
       <c r="E41" s="19" t="s">
         <v>8</v>

--- a/assets/inventory/excel/רשימה 2.xlsx
+++ b/assets/inventory/excel/רשימה 2.xlsx
@@ -1387,7 +1387,7 @@
         <v>46219</v>
       </c>
       <c r="E34" s="19" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="F34" s="22">
         <v>250</v>

--- a/assets/inventory/excel/רשימה 2.xlsx
+++ b/assets/inventory/excel/רשימה 2.xlsx
@@ -489,14 +489,14 @@
     <xf numFmtId="0" fontId="2" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1"/>
     <xf numFmtId="14" fontId="3" fillId="4" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -730,11 +730,11 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:11" ht="24" customHeight="1">
-      <c r="A1" s="24" t="s">
+      <c r="A1" s="26" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="25"/>
-      <c r="C1" s="25"/>
+      <c r="B1" s="27"/>
+      <c r="C1" s="27"/>
     </row>
     <row r="2" spans="1:11" ht="15" customHeight="1" thickBot="1">
       <c r="J2" s="12" t="s">
@@ -1147,7 +1147,7 @@
         <v>46219</v>
       </c>
       <c r="E22" s="19" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="F22" s="20">
         <v>230</v>
@@ -1187,7 +1187,7 @@
         <v>46219</v>
       </c>
       <c r="E24" s="19" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="F24" s="20">
         <v>230</v>
@@ -1247,7 +1247,7 @@
         <v>46219</v>
       </c>
       <c r="E27" s="18" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="F27" s="21">
         <v>330</v>
@@ -1267,7 +1267,7 @@
         <v>46219</v>
       </c>
       <c r="E28" s="19" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="F28" s="20">
         <v>270</v>
@@ -1287,7 +1287,7 @@
         <v>46219</v>
       </c>
       <c r="E29" s="18" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="F29" s="21">
         <v>330</v>
@@ -1307,63 +1307,63 @@
         <v>46219</v>
       </c>
       <c r="E30" s="19" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="F30" s="20">
         <v>300</v>
       </c>
     </row>
     <row r="31" spans="1:6">
-      <c r="A31" s="26" t="s">
+      <c r="A31" s="24" t="s">
         <v>52</v>
       </c>
-      <c r="B31" s="26" t="s">
+      <c r="B31" s="24" t="s">
         <v>64</v>
       </c>
-      <c r="C31" s="26">
+      <c r="C31" s="24">
         <v>32</v>
       </c>
-      <c r="D31" s="27">
+      <c r="D31" s="25">
         <v>46219</v>
       </c>
       <c r="E31" s="19" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="F31" s="22">
         <v>270</v>
       </c>
     </row>
     <row r="32" spans="1:6">
-      <c r="A32" s="26" t="s">
+      <c r="A32" s="24" t="s">
         <v>53</v>
       </c>
-      <c r="B32" s="26" t="s">
+      <c r="B32" s="24" t="s">
         <v>65</v>
       </c>
-      <c r="C32" s="26">
+      <c r="C32" s="24">
         <v>38</v>
       </c>
-      <c r="D32" s="27">
+      <c r="D32" s="25">
         <v>46219</v>
       </c>
       <c r="E32" s="19" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="F32" s="22">
         <v>270</v>
       </c>
     </row>
     <row r="33" spans="1:6">
-      <c r="A33" s="26" t="s">
+      <c r="A33" s="24" t="s">
         <v>54</v>
       </c>
-      <c r="B33" s="26" t="s">
+      <c r="B33" s="24" t="s">
         <v>66</v>
       </c>
-      <c r="C33" s="26">
+      <c r="C33" s="24">
         <v>30</v>
       </c>
-      <c r="D33" s="27">
+      <c r="D33" s="25">
         <v>46219</v>
       </c>
       <c r="E33" s="19" t="s">
@@ -1374,16 +1374,16 @@
       </c>
     </row>
     <row r="34" spans="1:6">
-      <c r="A34" s="26" t="s">
+      <c r="A34" s="24" t="s">
         <v>55</v>
       </c>
-      <c r="B34" s="26" t="s">
+      <c r="B34" s="24" t="s">
         <v>48</v>
       </c>
-      <c r="C34" s="26">
+      <c r="C34" s="24">
         <v>30</v>
       </c>
-      <c r="D34" s="27">
+      <c r="D34" s="25">
         <v>46219</v>
       </c>
       <c r="E34" s="19" t="s">
@@ -1394,16 +1394,16 @@
       </c>
     </row>
     <row r="35" spans="1:6">
-      <c r="A35" s="26" t="s">
+      <c r="A35" s="24" t="s">
         <v>56</v>
       </c>
-      <c r="B35" s="26" t="s">
+      <c r="B35" s="24" t="s">
         <v>67</v>
       </c>
-      <c r="C35" s="26">
+      <c r="C35" s="24">
         <v>34</v>
       </c>
-      <c r="D35" s="27">
+      <c r="D35" s="25">
         <v>46219</v>
       </c>
       <c r="E35" s="19" t="s">
@@ -1414,36 +1414,36 @@
       </c>
     </row>
     <row r="36" spans="1:6">
-      <c r="A36" s="26" t="s">
+      <c r="A36" s="24" t="s">
         <v>57</v>
       </c>
-      <c r="B36" s="26" t="s">
+      <c r="B36" s="24" t="s">
         <v>68</v>
       </c>
-      <c r="C36" s="26" t="s">
+      <c r="C36" s="24" t="s">
         <v>13</v>
       </c>
-      <c r="D36" s="27">
+      <c r="D36" s="25">
         <v>46219</v>
       </c>
       <c r="E36" s="19" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="F36" s="22">
         <v>270</v>
       </c>
     </row>
     <row r="37" spans="1:6">
-      <c r="A37" s="26" t="s">
+      <c r="A37" s="24" t="s">
         <v>58</v>
       </c>
-      <c r="B37" s="26" t="s">
+      <c r="B37" s="24" t="s">
         <v>48</v>
       </c>
-      <c r="C37" s="26">
+      <c r="C37" s="24">
         <v>32</v>
       </c>
-      <c r="D37" s="27">
+      <c r="D37" s="25">
         <v>46219</v>
       </c>
       <c r="E37" s="19" t="s">
@@ -1454,36 +1454,36 @@
       </c>
     </row>
     <row r="38" spans="1:6">
-      <c r="A38" s="26" t="s">
+      <c r="A38" s="24" t="s">
         <v>59</v>
       </c>
-      <c r="B38" s="26" t="s">
+      <c r="B38" s="24" t="s">
         <v>48</v>
       </c>
-      <c r="C38" s="26">
+      <c r="C38" s="24">
         <v>34</v>
       </c>
-      <c r="D38" s="27">
+      <c r="D38" s="25">
         <v>46219</v>
       </c>
       <c r="E38" s="19" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="F38" s="22">
         <v>270</v>
       </c>
     </row>
     <row r="39" spans="1:6">
-      <c r="A39" s="26" t="s">
+      <c r="A39" s="24" t="s">
         <v>60</v>
       </c>
-      <c r="B39" s="26" t="s">
+      <c r="B39" s="24" t="s">
         <v>46</v>
       </c>
-      <c r="C39" s="26">
+      <c r="C39" s="24">
         <v>38</v>
       </c>
-      <c r="D39" s="27">
+      <c r="D39" s="25">
         <v>46219</v>
       </c>
       <c r="E39" s="19" t="s">
@@ -1494,40 +1494,40 @@
       </c>
     </row>
     <row r="40" spans="1:6">
-      <c r="A40" s="26" t="s">
+      <c r="A40" s="24" t="s">
         <v>61</v>
       </c>
-      <c r="B40" s="26" t="s">
+      <c r="B40" s="24" t="s">
         <v>46</v>
       </c>
-      <c r="C40" s="26">
+      <c r="C40" s="24">
         <v>34</v>
       </c>
-      <c r="D40" s="27">
+      <c r="D40" s="25">
         <v>46219</v>
       </c>
       <c r="E40" s="19" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="F40" s="22">
         <v>270</v>
       </c>
     </row>
     <row r="41" spans="1:6">
-      <c r="A41" s="26" t="s">
+      <c r="A41" s="24" t="s">
         <v>62</v>
       </c>
-      <c r="B41" s="26" t="s">
+      <c r="B41" s="24" t="s">
         <v>46</v>
       </c>
-      <c r="C41" s="26">
+      <c r="C41" s="24">
         <v>29</v>
       </c>
-      <c r="D41" s="27">
+      <c r="D41" s="25">
         <v>46219</v>
       </c>
       <c r="E41" s="19" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="F41" s="22">
         <v>230</v>

--- a/assets/inventory/excel/רשימה 2.xlsx
+++ b/assets/inventory/excel/רשימה 2.xlsx
@@ -778,7 +778,7 @@
         <v>46217</v>
       </c>
       <c r="E4" s="19" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="F4" s="20">
         <v>150</v>

--- a/assets/inventory/excel/רשימה 2.xlsx
+++ b/assets/inventory/excel/רשימה 2.xlsx
@@ -867,7 +867,7 @@
         <v>46217</v>
       </c>
       <c r="E8" s="19" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="F8" s="20">
         <v>125</v>

--- a/assets/inventory/excel/רשימה 2.xlsx
+++ b/assets/inventory/excel/רשימה 2.xlsx
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="139" uniqueCount="69">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="179" uniqueCount="85">
   <si>
     <t>רשימת מכנסיים</t>
   </si>
@@ -239,6 +239,54 @@
   </si>
   <si>
     <t>MILITARY</t>
+  </si>
+  <si>
+    <t>#66</t>
+  </si>
+  <si>
+    <t>#67</t>
+  </si>
+  <si>
+    <t>#68</t>
+  </si>
+  <si>
+    <t>#69</t>
+  </si>
+  <si>
+    <t>#70</t>
+  </si>
+  <si>
+    <t>#71</t>
+  </si>
+  <si>
+    <t>#72</t>
+  </si>
+  <si>
+    <t>#73</t>
+  </si>
+  <si>
+    <t>#74</t>
+  </si>
+  <si>
+    <t>#75</t>
+  </si>
+  <si>
+    <t>#76</t>
+  </si>
+  <si>
+    <t>#77</t>
+  </si>
+  <si>
+    <t>M</t>
+  </si>
+  <si>
+    <t>GIRLS</t>
+  </si>
+  <si>
+    <t>ROXY</t>
+  </si>
+  <si>
+    <t>#78</t>
   </si>
 </sst>
 </file>
@@ -553,7 +601,7 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="PantsTable" displayName="PantsTable" ref="A3:D41">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="PantsTable" displayName="PantsTable" ref="A3:D54">
   <tableColumns count="4">
     <tableColumn id="1" name="מספר מכנס"/>
     <tableColumn id="2" name="שם מכנס"/>
@@ -715,7 +763,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:K41"/>
+  <dimension ref="A1:K54"/>
   <sheetFormatPr defaultRowHeight="14"/>
   <cols>
     <col min="1" max="1" width="15" customWidth="1"/>
@@ -1527,10 +1575,271 @@
         <v>46219</v>
       </c>
       <c r="E41" s="19" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="F41" s="22">
         <v>230</v>
+      </c>
+    </row>
+    <row r="42" spans="1:6">
+      <c r="A42" s="24" t="s">
+        <v>69</v>
+      </c>
+      <c r="B42" s="24" t="s">
+        <v>46</v>
+      </c>
+      <c r="C42" s="24" t="s">
+        <v>81</v>
+      </c>
+      <c r="D42" s="25">
+        <v>46225</v>
+      </c>
+      <c r="E42" s="19" t="s">
+        <v>8</v>
+      </c>
+      <c r="F42" s="22">
+        <v>250</v>
+      </c>
+    </row>
+    <row r="43" spans="1:6">
+      <c r="A43" s="24" t="s">
+        <v>70</v>
+      </c>
+      <c r="B43" t="s">
+        <v>46</v>
+      </c>
+      <c r="C43">
+        <v>36</v>
+      </c>
+      <c r="D43" s="16">
+        <v>46225</v>
+      </c>
+      <c r="E43" s="19" t="s">
+        <v>8</v>
+      </c>
+      <c r="F43" s="22">
+        <v>270</v>
+      </c>
+    </row>
+    <row r="44" spans="1:6">
+      <c r="A44" s="24" t="s">
+        <v>71</v>
+      </c>
+      <c r="B44" t="s">
+        <v>46</v>
+      </c>
+      <c r="C44">
+        <v>38</v>
+      </c>
+      <c r="D44" s="16">
+        <v>46225</v>
+      </c>
+      <c r="E44" s="19" t="s">
+        <v>8</v>
+      </c>
+      <c r="F44" s="22">
+        <v>290</v>
+      </c>
+    </row>
+    <row r="45" spans="1:6">
+      <c r="A45" s="24" t="s">
+        <v>72</v>
+      </c>
+      <c r="B45" t="s">
+        <v>15</v>
+      </c>
+      <c r="C45">
+        <v>34</v>
+      </c>
+      <c r="D45" s="16">
+        <v>46225</v>
+      </c>
+      <c r="E45" s="19" t="s">
+        <v>8</v>
+      </c>
+      <c r="F45" s="22">
+        <v>290</v>
+      </c>
+    </row>
+    <row r="46" spans="1:6">
+      <c r="A46" s="24" t="s">
+        <v>73</v>
+      </c>
+      <c r="B46" t="s">
+        <v>15</v>
+      </c>
+      <c r="C46">
+        <v>38</v>
+      </c>
+      <c r="D46" s="16">
+        <v>46225</v>
+      </c>
+      <c r="E46" s="19" t="s">
+        <v>8</v>
+      </c>
+      <c r="F46" s="22">
+        <v>280</v>
+      </c>
+    </row>
+    <row r="47" spans="1:6">
+      <c r="A47" s="24" t="s">
+        <v>74</v>
+      </c>
+      <c r="B47" s="24" t="s">
+        <v>46</v>
+      </c>
+      <c r="C47" s="24">
+        <v>32</v>
+      </c>
+      <c r="D47" s="25">
+        <v>46225</v>
+      </c>
+      <c r="E47" s="19" t="s">
+        <v>8</v>
+      </c>
+      <c r="F47" s="22">
+        <v>270</v>
+      </c>
+    </row>
+    <row r="48" spans="1:6">
+      <c r="A48" s="24" t="s">
+        <v>75</v>
+      </c>
+      <c r="B48" s="24" t="s">
+        <v>46</v>
+      </c>
+      <c r="C48" s="24">
+        <v>38</v>
+      </c>
+      <c r="D48" s="25">
+        <v>46225</v>
+      </c>
+      <c r="E48" s="19" t="s">
+        <v>8</v>
+      </c>
+      <c r="F48" s="22">
+        <v>250</v>
+      </c>
+    </row>
+    <row r="49" spans="1:6">
+      <c r="A49" s="24" t="s">
+        <v>76</v>
+      </c>
+      <c r="B49" s="24" t="s">
+        <v>82</v>
+      </c>
+      <c r="C49" s="24">
+        <v>26</v>
+      </c>
+      <c r="D49" s="25">
+        <v>46225</v>
+      </c>
+      <c r="E49" s="19" t="s">
+        <v>8</v>
+      </c>
+      <c r="F49" s="22">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="50" spans="1:6">
+      <c r="A50" s="24" t="s">
+        <v>77</v>
+      </c>
+      <c r="B50" s="24" t="s">
+        <v>83</v>
+      </c>
+      <c r="C50" s="24">
+        <v>34</v>
+      </c>
+      <c r="D50" s="25">
+        <v>46225</v>
+      </c>
+      <c r="E50" s="19" t="s">
+        <v>8</v>
+      </c>
+      <c r="F50" s="22">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="51" spans="1:6">
+      <c r="A51" s="24" t="s">
+        <v>78</v>
+      </c>
+      <c r="B51" s="24" t="s">
+        <v>46</v>
+      </c>
+      <c r="C51" s="24">
+        <v>34</v>
+      </c>
+      <c r="D51" s="25">
+        <v>46225</v>
+      </c>
+      <c r="E51" s="19" t="s">
+        <v>8</v>
+      </c>
+      <c r="F51" s="22">
+        <v>270</v>
+      </c>
+    </row>
+    <row r="52" spans="1:6">
+      <c r="A52" s="24" t="s">
+        <v>79</v>
+      </c>
+      <c r="B52" t="s">
+        <v>46</v>
+      </c>
+      <c r="C52">
+        <v>31</v>
+      </c>
+      <c r="D52" s="16">
+        <v>46225</v>
+      </c>
+      <c r="E52" s="19" t="s">
+        <v>8</v>
+      </c>
+      <c r="F52" s="22">
+        <v>250</v>
+      </c>
+    </row>
+    <row r="53" spans="1:6">
+      <c r="A53" s="24" t="s">
+        <v>80</v>
+      </c>
+      <c r="B53" t="s">
+        <v>46</v>
+      </c>
+      <c r="C53">
+        <v>36</v>
+      </c>
+      <c r="D53" s="16">
+        <v>46225</v>
+      </c>
+      <c r="E53" s="19" t="s">
+        <v>8</v>
+      </c>
+      <c r="F53" s="22">
+        <v>250</v>
+      </c>
+    </row>
+    <row r="54" spans="1:6">
+      <c r="A54" s="24" t="s">
+        <v>84</v>
+      </c>
+      <c r="B54" s="24" t="s">
+        <v>46</v>
+      </c>
+      <c r="C54" s="24">
+        <v>36</v>
+      </c>
+      <c r="D54" s="25">
+        <f>$K$2</f>
+        <v>46217</v>
+      </c>
+      <c r="E54" s="19" t="s">
+        <v>8</v>
+      </c>
+      <c r="F54" s="22">
+        <v>270</v>
       </c>
     </row>
   </sheetData>
@@ -1538,7 +1847,7 @@
     <mergeCell ref="A1:C1"/>
   </mergeCells>
   <dataValidations count="1">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E4:E41">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E4:E54">
       <formula1>$K$5:$K$6</formula1>
     </dataValidation>
   </dataValidations>

--- a/assets/inventory/excel/רשימה 2.xlsx
+++ b/assets/inventory/excel/רשימה 2.xlsx
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="179" uniqueCount="85">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="180" uniqueCount="86">
   <si>
     <t>רשימת מכנסיים</t>
   </si>
@@ -287,6 +287,9 @@
   </si>
   <si>
     <t>#78</t>
+  </si>
+  <si>
+    <t>#79</t>
   </si>
 </sst>
 </file>
@@ -601,7 +604,7 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="PantsTable" displayName="PantsTable" ref="A3:D54">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="PantsTable" displayName="PantsTable" ref="A3:D55">
   <tableColumns count="4">
     <tableColumn id="1" name="מספר מכנס"/>
     <tableColumn id="2" name="שם מכנס"/>
@@ -763,7 +766,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:K54"/>
+  <dimension ref="A1:K55"/>
   <sheetFormatPr defaultRowHeight="14"/>
   <cols>
     <col min="1" max="1" width="15" customWidth="1"/>
@@ -1832,14 +1835,24 @@
         <v>36</v>
       </c>
       <c r="D54" s="25">
+        <v>46225</v>
+      </c>
+      <c r="E54" s="19" t="s">
+        <v>8</v>
+      </c>
+      <c r="F54" s="22">
+        <v>270</v>
+      </c>
+    </row>
+    <row r="55" spans="1:6">
+      <c r="A55" s="24" t="s">
+        <v>85</v>
+      </c>
+      <c r="B55" s="24"/>
+      <c r="C55" s="24"/>
+      <c r="D55" s="25">
         <f>$K$2</f>
         <v>46217</v>
-      </c>
-      <c r="E54" s="19" t="s">
-        <v>8</v>
-      </c>
-      <c r="F54" s="22">
-        <v>270</v>
       </c>
     </row>
   </sheetData>

--- a/assets/inventory/excel/רשימה 2.xlsx
+++ b/assets/inventory/excel/רשימה 2.xlsx
@@ -1,12 +1,12 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="7812" yWindow="0" windowWidth="15324" windowHeight="12336" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="רשימת מכנסיים" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="רשימת מכנסיים" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="191029" fullCalcOnLoad="1"/>
@@ -502,7 +502,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K34"/>
+  <dimension ref="A1:K23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="13.8"/>
   <cols>
     <col width="15" customWidth="1" style="21" min="1" max="1"/>
@@ -746,90 +746,92 @@
     <row r="10" ht="16.8" customHeight="1" s="21">
       <c r="A10" s="5" t="inlineStr">
         <is>
-          <t>#39</t>
+          <t>#43</t>
         </is>
       </c>
       <c r="B10" s="4" t="inlineStr">
         <is>
-          <t>billabong</t>
-        </is>
-      </c>
-      <c r="C10" s="6" t="n">
-        <v>32</v>
+          <t>fire</t>
+        </is>
+      </c>
+      <c r="C10" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
       </c>
       <c r="D10" s="11" t="n">
         <v>46217</v>
       </c>
       <c r="E10" s="12" t="inlineStr">
         <is>
-          <t>נמכר</t>
+          <t>לא נמכר</t>
         </is>
       </c>
       <c r="F10" s="15" t="n">
-        <v>250</v>
+        <v>230</v>
       </c>
     </row>
     <row r="11" ht="16.8" customHeight="1" s="21">
       <c r="A11" s="5" t="inlineStr">
         <is>
-          <t>#41</t>
+          <t>#47</t>
         </is>
       </c>
       <c r="B11" s="4" t="inlineStr">
         <is>
-          <t>billabong</t>
+          <t>flowers</t>
         </is>
       </c>
       <c r="C11" s="6" t="n">
         <v>36</v>
       </c>
       <c r="D11" s="11" t="n">
-        <v>46217</v>
+        <v>46219</v>
       </c>
       <c r="E11" s="12" t="inlineStr">
         <is>
-          <t>נמכר</t>
+          <t>לא נמכר</t>
         </is>
       </c>
       <c r="F11" s="15" t="n">
-        <v>230</v>
+        <v>200</v>
       </c>
     </row>
     <row r="12" ht="16.8" customHeight="1" s="21">
       <c r="A12" s="5" t="inlineStr">
         <is>
-          <t>#42</t>
+          <t>#49</t>
         </is>
       </c>
       <c r="B12" s="4" t="inlineStr">
         <is>
-          <t>billabong</t>
+          <t>fire</t>
         </is>
       </c>
       <c r="C12" s="6" t="n">
-        <v>31</v>
-      </c>
-      <c r="D12" s="10" t="n">
-        <v>46217</v>
-      </c>
-      <c r="E12" s="13" t="inlineStr">
-        <is>
-          <t>נמכר</t>
-        </is>
-      </c>
-      <c r="F12" s="14" t="n">
-        <v>260</v>
+        <v>34</v>
+      </c>
+      <c r="D12" s="11" t="n">
+        <v>46219</v>
+      </c>
+      <c r="E12" s="12" t="inlineStr">
+        <is>
+          <t>לא נמכר</t>
+        </is>
+      </c>
+      <c r="F12" s="15" t="n">
+        <v>250</v>
       </c>
     </row>
     <row r="13" ht="16.8" customHeight="1" s="21">
       <c r="A13" s="5" t="inlineStr">
         <is>
-          <t>#43</t>
+          <t>#50</t>
         </is>
       </c>
       <c r="B13" s="4" t="inlineStr">
         <is>
-          <t>fire</t>
+          <t>flowers</t>
         </is>
       </c>
       <c r="C13" s="6" t="inlineStr">
@@ -837,166 +839,166 @@
           <t>L</t>
         </is>
       </c>
-      <c r="D13" s="11" t="n">
-        <v>46217</v>
-      </c>
-      <c r="E13" s="12" t="inlineStr">
-        <is>
-          <t>לא נמכר</t>
-        </is>
-      </c>
-      <c r="F13" s="15" t="n">
-        <v>230</v>
+      <c r="D13" s="10" t="n">
+        <v>46219</v>
+      </c>
+      <c r="E13" s="13" t="inlineStr">
+        <is>
+          <t>לא נמכר</t>
+        </is>
+      </c>
+      <c r="F13" s="14" t="n">
+        <v>200</v>
       </c>
     </row>
     <row r="14" ht="16.8" customHeight="1" s="21">
-      <c r="A14" s="5" t="inlineStr">
-        <is>
-          <t>#44</t>
-        </is>
-      </c>
-      <c r="B14" s="4" t="inlineStr">
+      <c r="A14" s="18" t="inlineStr">
+        <is>
+          <t>#57</t>
+        </is>
+      </c>
+      <c r="B14" s="18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">                  billabong</t>
+        </is>
+      </c>
+      <c r="C14" s="18" t="n">
+        <v>30</v>
+      </c>
+      <c r="D14" s="19" t="n">
+        <v>46219</v>
+      </c>
+      <c r="E14" s="13" t="inlineStr">
+        <is>
+          <t>לא נמכר</t>
+        </is>
+      </c>
+      <c r="F14" s="16" t="n">
+        <v>250</v>
+      </c>
+    </row>
+    <row r="15" ht="16.8" customHeight="1" s="21">
+      <c r="A15" s="18" t="inlineStr">
+        <is>
+          <t>#59</t>
+        </is>
+      </c>
+      <c r="B15" s="18" t="inlineStr">
+        <is>
+          <t>GRAY</t>
+        </is>
+      </c>
+      <c r="C15" s="18" t="n">
+        <v>34</v>
+      </c>
+      <c r="D15" s="19" t="n">
+        <v>46219</v>
+      </c>
+      <c r="E15" s="13" t="inlineStr">
+        <is>
+          <t>לא נמכר</t>
+        </is>
+      </c>
+      <c r="F15" s="16" t="n">
+        <v>250</v>
+      </c>
+    </row>
+    <row r="16" ht="16.8" customHeight="1" s="21">
+      <c r="A16" s="18" t="inlineStr">
+        <is>
+          <t>#61</t>
+        </is>
+      </c>
+      <c r="B16" s="18" t="inlineStr">
         <is>
           <t>oniell</t>
         </is>
       </c>
-      <c r="C14" s="6" t="n">
-        <v>36</v>
-      </c>
-      <c r="D14" s="10" t="n">
-        <v>46217</v>
-      </c>
-      <c r="E14" s="13" t="inlineStr">
-        <is>
-          <t>נמכר</t>
-        </is>
-      </c>
-      <c r="F14" s="14" t="n">
-        <v>260</v>
-      </c>
-    </row>
-    <row r="15" ht="16.8" customHeight="1" s="21">
-      <c r="A15" s="5" t="inlineStr">
-        <is>
-          <t>#45</t>
-        </is>
-      </c>
-      <c r="B15" s="4" t="inlineStr">
-        <is>
-          <t>blue</t>
-        </is>
-      </c>
-      <c r="C15" s="6" t="n">
-        <v>29</v>
-      </c>
-      <c r="D15" s="11" t="n">
+      <c r="C16" s="18" t="n">
+        <v>32</v>
+      </c>
+      <c r="D16" s="19" t="n">
         <v>46219</v>
       </c>
-      <c r="E15" s="12" t="inlineStr">
-        <is>
-          <t>נמכר</t>
-        </is>
-      </c>
-      <c r="F15" s="15" t="n">
-        <v>230</v>
-      </c>
-    </row>
-    <row r="16" ht="16.8" customHeight="1" s="21">
-      <c r="A16" s="5" t="inlineStr">
-        <is>
-          <t>#47</t>
-        </is>
-      </c>
-      <c r="B16" s="4" t="inlineStr">
-        <is>
-          <t>flowers</t>
-        </is>
-      </c>
-      <c r="C16" s="6" t="n">
-        <v>36</v>
-      </c>
-      <c r="D16" s="11" t="n">
+      <c r="E16" s="13" t="inlineStr">
+        <is>
+          <t>לא נמכר</t>
+        </is>
+      </c>
+      <c r="F16" s="16" t="n">
+        <v>270</v>
+      </c>
+    </row>
+    <row r="17" ht="16.8" customHeight="1" s="21">
+      <c r="A17" s="18" t="inlineStr">
+        <is>
+          <t>#63</t>
+        </is>
+      </c>
+      <c r="B17" s="18" t="inlineStr">
+        <is>
+          <t>billabong</t>
+        </is>
+      </c>
+      <c r="C17" s="18" t="n">
+        <v>38</v>
+      </c>
+      <c r="D17" s="19" t="n">
         <v>46219</v>
       </c>
-      <c r="E16" s="12" t="inlineStr">
-        <is>
-          <t>לא נמכר</t>
-        </is>
-      </c>
-      <c r="F16" s="15" t="n">
-        <v>200</v>
-      </c>
-    </row>
-    <row r="17" ht="16.8" customHeight="1" s="21">
-      <c r="A17" s="5" t="inlineStr">
-        <is>
-          <t>#49</t>
-        </is>
-      </c>
-      <c r="B17" s="4" t="inlineStr">
-        <is>
-          <t>fire</t>
-        </is>
-      </c>
-      <c r="C17" s="6" t="n">
-        <v>34</v>
-      </c>
-      <c r="D17" s="11" t="n">
-        <v>46219</v>
-      </c>
-      <c r="E17" s="12" t="inlineStr">
-        <is>
-          <t>לא נמכר</t>
-        </is>
-      </c>
-      <c r="F17" s="15" t="n">
+      <c r="E17" s="13" t="inlineStr">
+        <is>
+          <t>לא נמכר</t>
+        </is>
+      </c>
+      <c r="F17" s="16" t="n">
+        <v>270</v>
+      </c>
+    </row>
+    <row r="18" ht="16.8" customHeight="1" s="21">
+      <c r="A18" s="18" t="inlineStr">
+        <is>
+          <t>#66</t>
+        </is>
+      </c>
+      <c r="B18" s="18" t="inlineStr">
+        <is>
+          <t>billabong</t>
+        </is>
+      </c>
+      <c r="C18" s="18" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="D18" s="19" t="n">
+        <v>46225</v>
+      </c>
+      <c r="E18" s="13" t="inlineStr">
+        <is>
+          <t>לא נמכר</t>
+        </is>
+      </c>
+      <c r="F18" s="16" t="n">
         <v>250</v>
-      </c>
-    </row>
-    <row r="18" ht="16.8" customHeight="1" s="21">
-      <c r="A18" s="5" t="inlineStr">
-        <is>
-          <t>#50</t>
-        </is>
-      </c>
-      <c r="B18" s="4" t="inlineStr">
-        <is>
-          <t>flowers</t>
-        </is>
-      </c>
-      <c r="C18" s="6" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="D18" s="10" t="n">
-        <v>46219</v>
-      </c>
-      <c r="E18" s="13" t="inlineStr">
-        <is>
-          <t>לא נמכר</t>
-        </is>
-      </c>
-      <c r="F18" s="14" t="n">
-        <v>200</v>
       </c>
     </row>
     <row r="19" ht="16.8" customHeight="1" s="21">
       <c r="A19" s="18" t="inlineStr">
         <is>
-          <t>#57</t>
-        </is>
-      </c>
-      <c r="B19" s="18" t="inlineStr">
-        <is>
-          <t xml:space="preserve">                  billabong</t>
-        </is>
-      </c>
-      <c r="C19" s="18" t="n">
-        <v>30</v>
-      </c>
-      <c r="D19" s="19" t="n">
-        <v>46219</v>
+          <t>#70</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>QuickSilver</t>
+        </is>
+      </c>
+      <c r="C19" t="n">
+        <v>38</v>
+      </c>
+      <c r="D19" s="10" t="n">
+        <v>46225</v>
       </c>
       <c r="E19" s="13" t="inlineStr">
         <is>
@@ -1004,25 +1006,25 @@
         </is>
       </c>
       <c r="F19" s="16" t="n">
-        <v>250</v>
+        <v>280</v>
       </c>
     </row>
     <row r="20" ht="16.8" customHeight="1" s="21">
       <c r="A20" s="18" t="inlineStr">
         <is>
-          <t>#59</t>
+          <t>#71</t>
         </is>
       </c>
       <c r="B20" s="18" t="inlineStr">
         <is>
-          <t>GRAY</t>
+          <t>billabong</t>
         </is>
       </c>
       <c r="C20" s="18" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="D20" s="19" t="n">
-        <v>46219</v>
+        <v>46225</v>
       </c>
       <c r="E20" s="13" t="inlineStr">
         <is>
@@ -1030,25 +1032,25 @@
         </is>
       </c>
       <c r="F20" s="16" t="n">
-        <v>250</v>
+        <v>270</v>
       </c>
     </row>
     <row r="21" ht="16.8" customHeight="1" s="21">
       <c r="A21" s="18" t="inlineStr">
         <is>
-          <t>#61</t>
+          <t>#74</t>
         </is>
       </c>
       <c r="B21" s="18" t="inlineStr">
         <is>
-          <t>oniell</t>
+          <t>ROXY</t>
         </is>
       </c>
       <c r="C21" s="18" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="D21" s="19" t="n">
-        <v>46219</v>
+        <v>46225</v>
       </c>
       <c r="E21" s="13" t="inlineStr">
         <is>
@@ -1056,13 +1058,13 @@
         </is>
       </c>
       <c r="F21" s="16" t="n">
-        <v>270</v>
+        <v>240</v>
       </c>
     </row>
     <row r="22" ht="16.8" customHeight="1" s="21">
       <c r="A22" s="18" t="inlineStr">
         <is>
-          <t>#63</t>
+          <t>#78</t>
         </is>
       </c>
       <c r="B22" s="18" t="inlineStr">
@@ -1071,10 +1073,10 @@
         </is>
       </c>
       <c r="C22" s="18" t="n">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="D22" s="19" t="n">
-        <v>46219</v>
+        <v>46225</v>
       </c>
       <c r="E22" s="13" t="inlineStr">
         <is>
@@ -1088,304 +1090,23 @@
     <row r="23" ht="16.8" customHeight="1" s="21">
       <c r="A23" s="18" t="inlineStr">
         <is>
-          <t>#65</t>
-        </is>
-      </c>
-      <c r="B23" s="18" t="inlineStr">
-        <is>
-          <t>billabong</t>
-        </is>
-      </c>
-      <c r="C23" s="18" t="n">
-        <v>29</v>
-      </c>
-      <c r="D23" s="19" t="n">
-        <v>46219</v>
-      </c>
-      <c r="E23" s="13" t="inlineStr">
-        <is>
-          <t>נמכר</t>
-        </is>
-      </c>
-      <c r="F23" s="16" t="n">
-        <v>230</v>
-      </c>
-    </row>
-    <row r="24" ht="16.8" customHeight="1" s="21">
-      <c r="A24" s="18" t="inlineStr">
-        <is>
-          <t>#66</t>
-        </is>
-      </c>
-      <c r="B24" s="18" t="inlineStr">
-        <is>
-          <t>billabong</t>
-        </is>
-      </c>
-      <c r="C24" s="18" t="inlineStr">
-        <is>
-          <t>M</t>
-        </is>
-      </c>
-      <c r="D24" s="19" t="n">
-        <v>46225</v>
-      </c>
-      <c r="E24" s="13" t="inlineStr">
-        <is>
-          <t>לא נמכר</t>
-        </is>
-      </c>
-      <c r="F24" s="16" t="n">
-        <v>250</v>
-      </c>
-    </row>
-    <row r="25" ht="16.8" customHeight="1" s="21">
-      <c r="A25" s="18" t="inlineStr">
-        <is>
-          <t>#67</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>billabong</t>
-        </is>
-      </c>
-      <c r="C25" t="n">
-        <v>36</v>
-      </c>
-      <c r="D25" s="10" t="n">
-        <v>46225</v>
-      </c>
-      <c r="E25" s="13" t="inlineStr">
-        <is>
-          <t>נמכר</t>
-        </is>
-      </c>
-      <c r="F25" s="16" t="n">
-        <v>270</v>
-      </c>
-    </row>
-    <row r="26" ht="16.8" customHeight="1" s="21">
-      <c r="A26" s="18" t="inlineStr">
-        <is>
-          <t>#68</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>billabong</t>
-        </is>
-      </c>
-      <c r="C26" t="n">
-        <v>38</v>
-      </c>
-      <c r="D26" s="10" t="n">
-        <v>46225</v>
-      </c>
-      <c r="E26" s="13" t="inlineStr">
-        <is>
-          <t>נמכר</t>
-        </is>
-      </c>
-      <c r="F26" s="16" t="n">
-        <v>290</v>
-      </c>
-    </row>
-    <row r="27" ht="16.8" customHeight="1" s="21">
-      <c r="A27" s="18" t="inlineStr">
-        <is>
-          <t>#69</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>QuickSilver</t>
-        </is>
-      </c>
-      <c r="C27" t="n">
-        <v>34</v>
-      </c>
-      <c r="D27" s="10" t="n">
-        <v>46225</v>
-      </c>
-      <c r="E27" s="13" t="inlineStr">
-        <is>
-          <t>נמכר</t>
-        </is>
-      </c>
-      <c r="F27" s="16" t="n">
-        <v>290</v>
-      </c>
-    </row>
-    <row r="28" ht="16.8" customHeight="1" s="21">
-      <c r="A28" s="18" t="inlineStr">
-        <is>
-          <t>#70</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>QuickSilver</t>
-        </is>
-      </c>
-      <c r="C28" t="n">
-        <v>38</v>
-      </c>
-      <c r="D28" s="10" t="n">
-        <v>46225</v>
-      </c>
-      <c r="E28" s="13" t="inlineStr">
-        <is>
-          <t>לא נמכר</t>
-        </is>
-      </c>
-      <c r="F28" s="16" t="n">
-        <v>280</v>
-      </c>
-    </row>
-    <row r="29" ht="16.8" customHeight="1" s="21">
-      <c r="A29" s="18" t="inlineStr">
-        <is>
-          <t>#71</t>
-        </is>
-      </c>
-      <c r="B29" s="18" t="inlineStr">
-        <is>
-          <t>billabong</t>
-        </is>
-      </c>
-      <c r="C29" s="18" t="n">
-        <v>32</v>
-      </c>
-      <c r="D29" s="19" t="n">
-        <v>46225</v>
-      </c>
-      <c r="E29" s="13" t="inlineStr">
-        <is>
-          <t>לא נמכר</t>
-        </is>
-      </c>
-      <c r="F29" s="16" t="n">
-        <v>270</v>
-      </c>
-    </row>
-    <row r="30" ht="16.8" customHeight="1" s="21">
-      <c r="A30" s="18" t="inlineStr">
-        <is>
-          <t>#73</t>
-        </is>
-      </c>
-      <c r="B30" s="18" t="inlineStr">
-        <is>
-          <t>GIRLS</t>
-        </is>
-      </c>
-      <c r="C30" s="18" t="n">
-        <v>26</v>
-      </c>
-      <c r="D30" s="19" t="n">
-        <v>46225</v>
-      </c>
-      <c r="E30" s="13" t="inlineStr">
-        <is>
-          <t>נמכר</t>
-        </is>
-      </c>
-      <c r="F30" s="16" t="n">
-        <v>240</v>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" s="18" t="inlineStr">
-        <is>
-          <t>#74</t>
-        </is>
-      </c>
-      <c r="B31" s="18" t="inlineStr">
-        <is>
-          <t>ROXY</t>
-        </is>
-      </c>
-      <c r="C31" s="18" t="n">
-        <v>34</v>
-      </c>
-      <c r="D31" s="19" t="n">
-        <v>46225</v>
-      </c>
-      <c r="E31" s="13" t="inlineStr">
-        <is>
-          <t>לא נמכר</t>
-        </is>
-      </c>
-      <c r="F31" s="16" t="n">
-        <v>240</v>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" s="18" t="inlineStr">
-        <is>
-          <t>#75</t>
-        </is>
-      </c>
-      <c r="B32" s="18" t="inlineStr">
-        <is>
-          <t>billabong</t>
-        </is>
-      </c>
-      <c r="C32" s="18" t="n">
-        <v>34</v>
-      </c>
-      <c r="D32" s="19" t="n">
-        <v>46225</v>
-      </c>
-      <c r="E32" s="13" t="inlineStr">
-        <is>
-          <t>נמכר</t>
-        </is>
-      </c>
-      <c r="F32" s="16" t="n">
-        <v>270</v>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" s="18" t="inlineStr">
-        <is>
-          <t>#78</t>
-        </is>
-      </c>
-      <c r="B33" s="18" t="inlineStr">
-        <is>
-          <t>billabong</t>
-        </is>
-      </c>
-      <c r="C33" s="18" t="n">
-        <v>36</v>
-      </c>
-      <c r="D33" s="19" t="n">
-        <v>46225</v>
-      </c>
-      <c r="E33" s="13" t="inlineStr">
-        <is>
-          <t>לא נמכר</t>
-        </is>
-      </c>
-      <c r="F33" s="16" t="n">
-        <v>270</v>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" s="18" t="inlineStr">
-        <is>
           <t>#79</t>
         </is>
       </c>
-      <c r="B34" s="18" t="n"/>
-      <c r="C34" s="18" t="n"/>
-      <c r="D34" s="19">
+      <c r="B23" s="18" t="n"/>
+      <c r="C23" s="18" t="n"/>
+      <c r="D23" s="19">
         <f>$K$2</f>
         <v/>
       </c>
     </row>
+    <row r="24" ht="16.8" customHeight="1" s="21"/>
+    <row r="25" ht="16.8" customHeight="1" s="21"/>
+    <row r="26" ht="16.8" customHeight="1" s="21"/>
+    <row r="27" ht="16.8" customHeight="1" s="21"/>
+    <row r="28" ht="16.8" customHeight="1" s="21"/>
+    <row r="29" ht="16.8" customHeight="1" s="21"/>
+    <row r="30" ht="16.8" customHeight="1" s="21"/>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A1:C1"/>
